--- a/預測結果與評估指標_kfold_mask幾何_長邊正規化_年齡.xlsx
+++ b/預測結果與評估指標_kfold_mask幾何_長邊正規化_年齡.xlsx
@@ -490,28 +490,28 @@
         <v>69</v>
       </c>
       <c r="C2" s="0">
-        <v>603.14869999999996</v>
+        <v>606.4973</v>
       </c>
       <c r="D2" s="0">
         <v>23</v>
       </c>
       <c r="E2" s="0">
-        <v>20.10398340433359</v>
+        <v>20.135660141072528</v>
       </c>
       <c r="F2" s="0">
-        <v>-2.8960165956664099</v>
+        <v>-2.8643398589274724</v>
       </c>
       <c r="G2" s="0">
-        <v>2.8960165956664099</v>
+        <v>2.8643398589274724</v>
       </c>
       <c r="H2" s="0">
-        <v>19.60398340433359</v>
+        <v>19.635660141072528</v>
       </c>
       <c r="I2" s="0">
-        <v>-3.3960165956664099</v>
+        <v>-3.3643398589274725</v>
       </c>
       <c r="J2" s="0">
-        <v>3.3960165956664099</v>
+        <v>3.3643398589274725</v>
       </c>
       <c r="K2" s="0" t="b">
         <v>0</v>
@@ -534,28 +534,28 @@
         <v>69</v>
       </c>
       <c r="C3" s="0">
-        <v>605.62289999999996</v>
+        <v>609.20730000000003</v>
       </c>
       <c r="D3" s="0">
         <v>21</v>
       </c>
       <c r="E3" s="0">
-        <v>20.486835410687196</v>
+        <v>20.437494320769254</v>
       </c>
       <c r="F3" s="0">
-        <v>-0.51316458931280451</v>
+        <v>-0.56250567923074613</v>
       </c>
       <c r="G3" s="0">
-        <v>0.51316458931280451</v>
+        <v>0.56250567923074613</v>
       </c>
       <c r="H3" s="0">
-        <v>19.986835410687196</v>
+        <v>19.937494320769254</v>
       </c>
       <c r="I3" s="0">
-        <v>-1.0131645893128045</v>
+        <v>-1.0625056792307461</v>
       </c>
       <c r="J3" s="0">
-        <v>1.0131645893128045</v>
+        <v>1.0625056792307461</v>
       </c>
       <c r="K3" s="0" t="b">
         <v>0</v>
@@ -578,28 +578,28 @@
         <v>69</v>
       </c>
       <c r="C4" s="0">
-        <v>773.59109999999998</v>
+        <v>755.06500000000005</v>
       </c>
       <c r="D4" s="0">
         <v>23.5</v>
       </c>
       <c r="E4" s="0">
-        <v>23.762521214206352</v>
+        <v>23.649640433416977</v>
       </c>
       <c r="F4" s="0">
-        <v>0.26252121420635177</v>
+        <v>0.14964043341697675</v>
       </c>
       <c r="G4" s="0">
-        <v>0.26252121420635177</v>
+        <v>0.14964043341697675</v>
       </c>
       <c r="H4" s="0">
-        <v>23.262521214206352</v>
+        <v>23.149640433416977</v>
       </c>
       <c r="I4" s="0">
-        <v>-0.23747878579364823</v>
+        <v>-0.35035956658302325</v>
       </c>
       <c r="J4" s="0">
-        <v>0.23747878579364823</v>
+        <v>0.35035956658302325</v>
       </c>
       <c r="K4" s="0" t="b">
         <v>0</v>
@@ -622,28 +622,28 @@
         <v>69</v>
       </c>
       <c r="C5" s="0">
-        <v>579.42529999999999</v>
+        <v>579.86080000000004</v>
       </c>
       <c r="D5" s="0">
         <v>21</v>
       </c>
       <c r="E5" s="0">
-        <v>19.535477522075293</v>
+        <v>19.525907231108818</v>
       </c>
       <c r="F5" s="0">
-        <v>-1.4645224779247066</v>
+        <v>-1.4740927688911825</v>
       </c>
       <c r="G5" s="0">
-        <v>1.4645224779247066</v>
+        <v>1.4740927688911825</v>
       </c>
       <c r="H5" s="0">
-        <v>19.035477522075293</v>
+        <v>19.025907231108818</v>
       </c>
       <c r="I5" s="0">
-        <v>-1.9645224779247066</v>
+        <v>-1.9740927688911825</v>
       </c>
       <c r="J5" s="0">
-        <v>1.9645224779247066</v>
+        <v>1.9740927688911825</v>
       </c>
       <c r="K5" s="0" t="b">
         <v>0</v>
@@ -666,28 +666,28 @@
         <v>69</v>
       </c>
       <c r="C6" s="0">
-        <v>632.08730000000003</v>
+        <v>634.26990000000001</v>
       </c>
       <c r="D6" s="0">
         <v>21.5</v>
       </c>
       <c r="E6" s="0">
-        <v>21.095572785624231</v>
+        <v>21.006087195620292</v>
       </c>
       <c r="F6" s="0">
-        <v>-0.40442721437576878</v>
+        <v>-0.49391280437970764</v>
       </c>
       <c r="G6" s="0">
-        <v>0.40442721437576878</v>
+        <v>0.49391280437970764</v>
       </c>
       <c r="H6" s="0">
-        <v>20.595572785624231</v>
+        <v>20.506087195620292</v>
       </c>
       <c r="I6" s="0">
-        <v>-0.90442721437576879</v>
+        <v>-0.99391280437970764</v>
       </c>
       <c r="J6" s="0">
-        <v>0.90442721437576879</v>
+        <v>0.99391280437970764</v>
       </c>
       <c r="K6" s="0" t="b">
         <v>0</v>
@@ -710,31 +710,31 @@
         <v>69</v>
       </c>
       <c r="C7" s="0">
-        <v>720.98979999999995</v>
+        <v>691.86599999999999</v>
       </c>
       <c r="D7" s="0">
         <v>22</v>
       </c>
       <c r="E7" s="0">
-        <v>22.688886844003623</v>
+        <v>21.954646683499217</v>
       </c>
       <c r="F7" s="0">
-        <v>0.68888684400362266</v>
+        <v>-0.045353316500783336</v>
       </c>
       <c r="G7" s="0">
-        <v>0.68888684400362266</v>
+        <v>0.045353316500783336</v>
       </c>
       <c r="H7" s="0">
-        <v>22.188886844003623</v>
+        <v>21.454646683499217</v>
       </c>
       <c r="I7" s="0">
-        <v>0.18888684400362266</v>
+        <v>-0.54535331650078334</v>
       </c>
       <c r="J7" s="0">
-        <v>0.18888684400362266</v>
+        <v>0.54535331650078334</v>
       </c>
       <c r="K7" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="0">
         <v>5</v>
@@ -754,28 +754,28 @@
         <v>69</v>
       </c>
       <c r="C8" s="0">
-        <v>758.05489999999998</v>
+        <v>763.82230000000004</v>
       </c>
       <c r="D8" s="0">
         <v>25</v>
       </c>
       <c r="E8" s="0">
-        <v>23.228660804069808</v>
+        <v>23.408087539604697</v>
       </c>
       <c r="F8" s="0">
-        <v>-1.7713391959301923</v>
+        <v>-1.591912460395303</v>
       </c>
       <c r="G8" s="0">
-        <v>1.7713391959301923</v>
+        <v>1.591912460395303</v>
       </c>
       <c r="H8" s="0">
-        <v>22.728660804069808</v>
+        <v>22.908087539604697</v>
       </c>
       <c r="I8" s="0">
-        <v>-2.2713391959301923</v>
+        <v>-2.091912460395303</v>
       </c>
       <c r="J8" s="0">
-        <v>2.2713391959301923</v>
+        <v>2.091912460395303</v>
       </c>
       <c r="K8" s="0" t="b">
         <v>0</v>
@@ -798,28 +798,28 @@
         <v>69</v>
       </c>
       <c r="C9" s="0">
-        <v>607.71310000000005</v>
+        <v>612.55169999999998</v>
       </c>
       <c r="D9" s="0">
         <v>20.5</v>
       </c>
       <c r="E9" s="0">
-        <v>20.044482952846558</v>
+        <v>20.073128430802438</v>
       </c>
       <c r="F9" s="0">
-        <v>-0.45551704715344243</v>
+        <v>-0.4268715691975622</v>
       </c>
       <c r="G9" s="0">
-        <v>0.45551704715344243</v>
+        <v>0.4268715691975622</v>
       </c>
       <c r="H9" s="0">
-        <v>19.544482952846558</v>
+        <v>19.573128430802438</v>
       </c>
       <c r="I9" s="0">
-        <v>-0.95551704715344243</v>
+        <v>-0.9268715691975622</v>
       </c>
       <c r="J9" s="0">
-        <v>0.95551704715344243</v>
+        <v>0.9268715691975622</v>
       </c>
       <c r="K9" s="0" t="b">
         <v>0</v>
@@ -842,28 +842,28 @@
         <v>69</v>
       </c>
       <c r="C10" s="0">
-        <v>641.99860000000001</v>
+        <v>647.83249999999998</v>
       </c>
       <c r="D10" s="0">
         <v>21</v>
       </c>
       <c r="E10" s="0">
-        <v>20.818077489616748</v>
+        <v>20.852009792322242</v>
       </c>
       <c r="F10" s="0">
-        <v>-0.18192251038325225</v>
+        <v>-0.14799020767775772</v>
       </c>
       <c r="G10" s="0">
-        <v>0.18192251038325225</v>
+        <v>0.14799020767775772</v>
       </c>
       <c r="H10" s="0">
-        <v>20.318077489616748</v>
+        <v>20.352009792322242</v>
       </c>
       <c r="I10" s="0">
-        <v>-0.68192251038325224</v>
+        <v>-0.64799020767775772</v>
       </c>
       <c r="J10" s="0">
-        <v>0.68192251038325224</v>
+        <v>0.64799020767775772</v>
       </c>
       <c r="K10" s="0" t="b">
         <v>0</v>
@@ -886,28 +886,28 @@
         <v>69</v>
       </c>
       <c r="C11" s="0">
-        <v>463.59699999999998</v>
+        <v>468.75369999999998</v>
       </c>
       <c r="D11" s="0">
         <v>18</v>
       </c>
       <c r="E11" s="0">
-        <v>19.061127861295109</v>
+        <v>19.081603298059882</v>
       </c>
       <c r="F11" s="0">
-        <v>1.061127861295109</v>
+        <v>1.081603298059882</v>
       </c>
       <c r="G11" s="0">
-        <v>1.061127861295109</v>
+        <v>1.081603298059882</v>
       </c>
       <c r="H11" s="0">
-        <v>18.561127861295109</v>
+        <v>18.581603298059882</v>
       </c>
       <c r="I11" s="0">
-        <v>0.56112786129510894</v>
+        <v>0.58160329805988198</v>
       </c>
       <c r="J11" s="0">
-        <v>0.56112786129510894</v>
+        <v>0.58160329805988198</v>
       </c>
       <c r="K11" s="0" t="b">
         <v>1</v>
@@ -930,28 +930,28 @@
         <v>69</v>
       </c>
       <c r="C12" s="0">
-        <v>750.11170000000004</v>
+        <v>745.02800000000002</v>
       </c>
       <c r="D12" s="0">
         <v>25</v>
       </c>
       <c r="E12" s="0">
-        <v>24.197961398533856</v>
+        <v>24.108970527581022</v>
       </c>
       <c r="F12" s="0">
-        <v>-0.80203860146614403</v>
+        <v>-0.89102947241897823</v>
       </c>
       <c r="G12" s="0">
-        <v>0.80203860146614403</v>
+        <v>0.89102947241897823</v>
       </c>
       <c r="H12" s="0">
-        <v>23.697961398533856</v>
+        <v>23.608970527581022</v>
       </c>
       <c r="I12" s="0">
-        <v>-1.302038601466144</v>
+        <v>-1.3910294724189782</v>
       </c>
       <c r="J12" s="0">
-        <v>1.302038601466144</v>
+        <v>1.3910294724189782</v>
       </c>
       <c r="K12" s="0" t="b">
         <v>0</v>
@@ -974,28 +974,28 @@
         <v>69</v>
       </c>
       <c r="C13" s="0">
-        <v>675.26099999999997</v>
+        <v>674.10310000000004</v>
       </c>
       <c r="D13" s="0">
         <v>22.5</v>
       </c>
       <c r="E13" s="0">
-        <v>21.832092996059906</v>
+        <v>21.754731044735514</v>
       </c>
       <c r="F13" s="0">
-        <v>-0.66790700394009406</v>
+        <v>-0.74526895526448556</v>
       </c>
       <c r="G13" s="0">
-        <v>0.66790700394009406</v>
+        <v>0.74526895526448556</v>
       </c>
       <c r="H13" s="0">
-        <v>21.332092996059906</v>
+        <v>21.254731044735514</v>
       </c>
       <c r="I13" s="0">
-        <v>-1.1679070039400941</v>
+        <v>-1.2452689552644856</v>
       </c>
       <c r="J13" s="0">
-        <v>1.1679070039400941</v>
+        <v>1.2452689552644856</v>
       </c>
       <c r="K13" s="0" t="b">
         <v>0</v>
@@ -1018,28 +1018,28 @@
         <v>69</v>
       </c>
       <c r="C14" s="0">
-        <v>674.45989999999995</v>
+        <v>678.64329999999995</v>
       </c>
       <c r="D14" s="0">
         <v>20.5</v>
       </c>
       <c r="E14" s="0">
-        <v>21.050239246582564</v>
+        <v>21.018563239881459</v>
       </c>
       <c r="F14" s="0">
-        <v>0.55023924658256362</v>
+        <v>0.51856323988145903</v>
       </c>
       <c r="G14" s="0">
-        <v>0.55023924658256362</v>
+        <v>0.51856323988145903</v>
       </c>
       <c r="H14" s="0">
-        <v>20.550239246582564</v>
+        <v>20.518563239881459</v>
       </c>
       <c r="I14" s="0">
-        <v>0.050239246582563624</v>
+        <v>0.018563239881459026</v>
       </c>
       <c r="J14" s="0">
-        <v>0.050239246582563624</v>
+        <v>0.018563239881459026</v>
       </c>
       <c r="K14" s="0" t="b">
         <v>1</v>
@@ -1062,28 +1062,28 @@
         <v>69</v>
       </c>
       <c r="C15" s="0">
-        <v>583.64300000000003</v>
+        <v>588.29200000000003</v>
       </c>
       <c r="D15" s="0">
         <v>19.5</v>
       </c>
       <c r="E15" s="0">
-        <v>20.368659026889883</v>
+        <v>20.434352475485877</v>
       </c>
       <c r="F15" s="0">
-        <v>0.86865902688988328</v>
+        <v>0.93435247548587697</v>
       </c>
       <c r="G15" s="0">
-        <v>0.86865902688988328</v>
+        <v>0.93435247548587697</v>
       </c>
       <c r="H15" s="0">
-        <v>19.868659026889883</v>
+        <v>19.934352475485877</v>
       </c>
       <c r="I15" s="0">
-        <v>0.36865902688988328</v>
+        <v>0.43435247548587697</v>
       </c>
       <c r="J15" s="0">
-        <v>0.36865902688988328</v>
+        <v>0.43435247548587697</v>
       </c>
       <c r="K15" s="0" t="b">
         <v>1</v>
@@ -1106,28 +1106,28 @@
         <v>69</v>
       </c>
       <c r="C16" s="0">
-        <v>617.06880000000001</v>
+        <v>618.86260000000004</v>
       </c>
       <c r="D16" s="0">
         <v>19.5</v>
       </c>
       <c r="E16" s="0">
-        <v>20.68384283428783</v>
+        <v>20.598080545242858</v>
       </c>
       <c r="F16" s="0">
-        <v>1.1838428342878302</v>
+        <v>1.0980805452428584</v>
       </c>
       <c r="G16" s="0">
-        <v>1.1838428342878302</v>
+        <v>1.0980805452428584</v>
       </c>
       <c r="H16" s="0">
-        <v>20.18384283428783</v>
+        <v>20.098080545242858</v>
       </c>
       <c r="I16" s="0">
-        <v>0.68384283428783022</v>
+        <v>0.59808054524285836</v>
       </c>
       <c r="J16" s="0">
-        <v>0.68384283428783022</v>
+        <v>0.59808054524285836</v>
       </c>
       <c r="K16" s="0" t="b">
         <v>1</v>
@@ -1150,28 +1150,28 @@
         <v>69</v>
       </c>
       <c r="C17" s="0">
-        <v>565.14229999999998</v>
+        <v>557.87480000000005</v>
       </c>
       <c r="D17" s="0">
         <v>18.5</v>
       </c>
       <c r="E17" s="0">
-        <v>19.518889074827946</v>
+        <v>19.380567479822062</v>
       </c>
       <c r="F17" s="0">
-        <v>1.0188890748279462</v>
+        <v>0.88056747982206218</v>
       </c>
       <c r="G17" s="0">
-        <v>1.0188890748279462</v>
+        <v>0.88056747982206218</v>
       </c>
       <c r="H17" s="0">
-        <v>19.018889074827946</v>
+        <v>18.880567479822062</v>
       </c>
       <c r="I17" s="0">
-        <v>0.51888907482794622</v>
+        <v>0.38056747982206218</v>
       </c>
       <c r="J17" s="0">
-        <v>0.51888907482794622</v>
+        <v>0.38056747982206218</v>
       </c>
       <c r="K17" s="0" t="b">
         <v>1</v>
@@ -1194,28 +1194,28 @@
         <v>69</v>
       </c>
       <c r="C18" s="0">
-        <v>726.14229999999998</v>
+        <v>734.02059999999995</v>
       </c>
       <c r="D18" s="0">
         <v>23.75</v>
       </c>
       <c r="E18" s="0">
-        <v>23.450180467930409</v>
+        <v>23.74044211134467</v>
       </c>
       <c r="F18" s="0">
-        <v>-0.29981953206959133</v>
+        <v>-0.0095578886553298048</v>
       </c>
       <c r="G18" s="0">
-        <v>0.29981953206959133</v>
+        <v>0.0095578886553298048</v>
       </c>
       <c r="H18" s="0">
-        <v>22.950180467930409</v>
+        <v>23.24044211134467</v>
       </c>
       <c r="I18" s="0">
-        <v>-0.79981953206959133</v>
+        <v>-0.5095578886553298</v>
       </c>
       <c r="J18" s="0">
-        <v>0.79981953206959133</v>
+        <v>0.5095578886553298</v>
       </c>
       <c r="K18" s="0" t="b">
         <v>0</v>
@@ -1238,28 +1238,28 @@
         <v>69</v>
       </c>
       <c r="C19" s="0">
-        <v>668.60829999999999</v>
+        <v>674.8356</v>
       </c>
       <c r="D19" s="0">
         <v>22.25</v>
       </c>
       <c r="E19" s="0">
-        <v>21.098189920262428</v>
+        <v>21.183006688972888</v>
       </c>
       <c r="F19" s="0">
-        <v>-1.1518100797375723</v>
+        <v>-1.0669933110271117</v>
       </c>
       <c r="G19" s="0">
-        <v>1.1518100797375723</v>
+        <v>1.0669933110271117</v>
       </c>
       <c r="H19" s="0">
-        <v>20.598189920262428</v>
+        <v>20.683006688972888</v>
       </c>
       <c r="I19" s="0">
-        <v>-1.6518100797375723</v>
+        <v>-1.5669933110271117</v>
       </c>
       <c r="J19" s="0">
-        <v>1.6518100797375723</v>
+        <v>1.5669933110271117</v>
       </c>
       <c r="K19" s="0" t="b">
         <v>0</v>
@@ -1282,28 +1282,28 @@
         <v>69</v>
       </c>
       <c r="C20" s="0">
-        <v>750.32280000000003</v>
+        <v>758.93589999999995</v>
       </c>
       <c r="D20" s="0">
         <v>25.5</v>
       </c>
       <c r="E20" s="0">
-        <v>23.241963293449309</v>
+        <v>23.404956077111652</v>
       </c>
       <c r="F20" s="0">
-        <v>-2.2580367065506906</v>
+        <v>-2.0950439228883475</v>
       </c>
       <c r="G20" s="0">
-        <v>2.2580367065506906</v>
+        <v>2.0950439228883475</v>
       </c>
       <c r="H20" s="0">
-        <v>22.741963293449309</v>
+        <v>22.904956077111652</v>
       </c>
       <c r="I20" s="0">
-        <v>-2.7580367065506906</v>
+        <v>-2.5950439228883475</v>
       </c>
       <c r="J20" s="0">
-        <v>2.7580367065506906</v>
+        <v>2.5950439228883475</v>
       </c>
       <c r="K20" s="0" t="b">
         <v>0</v>
@@ -1326,28 +1326,28 @@
         <v>69</v>
       </c>
       <c r="C21" s="0">
-        <v>526.39779999999996</v>
+        <v>530.03160000000003</v>
       </c>
       <c r="D21" s="0">
         <v>22.5</v>
       </c>
       <c r="E21" s="0">
-        <v>18.368255354029387</v>
+        <v>18.417233331085964</v>
       </c>
       <c r="F21" s="0">
-        <v>-4.1317446459706133</v>
+        <v>-4.0827666689140365</v>
       </c>
       <c r="G21" s="0">
-        <v>4.1317446459706133</v>
+        <v>4.0827666689140365</v>
       </c>
       <c r="H21" s="0">
-        <v>17.868255354029387</v>
+        <v>17.917233331085964</v>
       </c>
       <c r="I21" s="0">
-        <v>-4.6317446459706133</v>
+        <v>-4.5827666689140365</v>
       </c>
       <c r="J21" s="0">
-        <v>4.6317446459706133</v>
+        <v>4.5827666689140365</v>
       </c>
       <c r="K21" s="0" t="b">
         <v>0</v>
@@ -1370,28 +1370,28 @@
         <v>69</v>
       </c>
       <c r="C22" s="0">
-        <v>622.22630000000004</v>
+        <v>619.3691</v>
       </c>
       <c r="D22" s="0">
         <v>21.5</v>
       </c>
       <c r="E22" s="0">
-        <v>20.231161133055519</v>
+        <v>20.115831115231142</v>
       </c>
       <c r="F22" s="0">
-        <v>-1.2688388669444812</v>
+        <v>-1.384168884768858</v>
       </c>
       <c r="G22" s="0">
-        <v>1.2688388669444812</v>
+        <v>1.384168884768858</v>
       </c>
       <c r="H22" s="0">
-        <v>19.731161133055519</v>
+        <v>19.615831115231142</v>
       </c>
       <c r="I22" s="0">
-        <v>-1.7688388669444812</v>
+        <v>-1.884168884768858</v>
       </c>
       <c r="J22" s="0">
-        <v>1.7688388669444812</v>
+        <v>1.884168884768858</v>
       </c>
       <c r="K22" s="0" t="b">
         <v>0</v>
@@ -1414,28 +1414,28 @@
         <v>69</v>
       </c>
       <c r="C23" s="0">
-        <v>671.48209999999995</v>
+        <v>681.04340000000002</v>
       </c>
       <c r="D23" s="0">
         <v>20</v>
       </c>
       <c r="E23" s="0">
-        <v>21.758855661980874</v>
+        <v>21.914699154633759</v>
       </c>
       <c r="F23" s="0">
-        <v>1.7588556619808742</v>
+        <v>1.9146991546337588</v>
       </c>
       <c r="G23" s="0">
-        <v>1.7588556619808742</v>
+        <v>1.9146991546337588</v>
       </c>
       <c r="H23" s="0">
-        <v>21.258855661980874</v>
+        <v>21.414699154633759</v>
       </c>
       <c r="I23" s="0">
-        <v>1.2588556619808742</v>
+        <v>1.4146991546337588</v>
       </c>
       <c r="J23" s="0">
-        <v>1.2588556619808742</v>
+        <v>1.4146991546337588</v>
       </c>
       <c r="K23" s="0" t="b">
         <v>1</v>
@@ -1458,28 +1458,28 @@
         <v>69</v>
       </c>
       <c r="C24" s="0">
-        <v>582.96010000000001</v>
+        <v>585.4384</v>
       </c>
       <c r="D24" s="0">
         <v>19.5</v>
       </c>
       <c r="E24" s="0">
-        <v>19.939928898913156</v>
+        <v>19.909019532292973</v>
       </c>
       <c r="F24" s="0">
-        <v>0.43992889891315556</v>
+        <v>0.40901953229297305</v>
       </c>
       <c r="G24" s="0">
-        <v>0.43992889891315556</v>
+        <v>0.40901953229297305</v>
       </c>
       <c r="H24" s="0">
-        <v>19.439928898913156</v>
+        <v>19.409019532292973</v>
       </c>
       <c r="I24" s="0">
-        <v>-0.060071101086844436</v>
+        <v>-0.090980467707026946</v>
       </c>
       <c r="J24" s="0">
-        <v>0.060071101086844436</v>
+        <v>0.090980467707026946</v>
       </c>
       <c r="K24" s="0" t="b">
         <v>0</v>
@@ -1502,28 +1502,28 @@
         <v>69</v>
       </c>
       <c r="C25" s="0">
-        <v>577.6952</v>
+        <v>581.173</v>
       </c>
       <c r="D25" s="0">
         <v>18.5</v>
       </c>
       <c r="E25" s="0">
-        <v>19.933677509114528</v>
+        <v>19.968785104804574</v>
       </c>
       <c r="F25" s="0">
-        <v>1.4336775091145277</v>
+        <v>1.4687851048045744</v>
       </c>
       <c r="G25" s="0">
-        <v>1.4336775091145277</v>
+        <v>1.4687851048045744</v>
       </c>
       <c r="H25" s="0">
-        <v>19.433677509114528</v>
+        <v>19.468785104804574</v>
       </c>
       <c r="I25" s="0">
-        <v>0.93367750911452774</v>
+        <v>0.96878510480457436</v>
       </c>
       <c r="J25" s="0">
-        <v>0.93367750911452774</v>
+        <v>0.96878510480457436</v>
       </c>
       <c r="K25" s="0" t="b">
         <v>1</v>
@@ -1546,28 +1546,28 @@
         <v>69</v>
       </c>
       <c r="C26" s="0">
-        <v>689.21019999999999</v>
+        <v>692.99239999999998</v>
       </c>
       <c r="D26" s="0">
         <v>21.25</v>
       </c>
       <c r="E26" s="0">
-        <v>22.436379342919885</v>
+        <v>22.268747188421543</v>
       </c>
       <c r="F26" s="0">
-        <v>1.186379342919885</v>
+        <v>1.0187471884215427</v>
       </c>
       <c r="G26" s="0">
-        <v>1.186379342919885</v>
+        <v>1.0187471884215427</v>
       </c>
       <c r="H26" s="0">
-        <v>21.936379342919885</v>
+        <v>21.768747188421543</v>
       </c>
       <c r="I26" s="0">
-        <v>0.68637934291988501</v>
+        <v>0.51874718842154266</v>
       </c>
       <c r="J26" s="0">
-        <v>0.68637934291988501</v>
+        <v>0.51874718842154266</v>
       </c>
       <c r="K26" s="0" t="b">
         <v>1</v>
@@ -1590,28 +1590,28 @@
         <v>69</v>
       </c>
       <c r="C27" s="0">
-        <v>641.4787</v>
+        <v>643.06439999999998</v>
       </c>
       <c r="D27" s="0">
         <v>19.25</v>
       </c>
       <c r="E27" s="0">
-        <v>20.816419688200963</v>
+        <v>20.745212692539834</v>
       </c>
       <c r="F27" s="0">
-        <v>1.5664196882009627</v>
+        <v>1.4952126925398339</v>
       </c>
       <c r="G27" s="0">
-        <v>1.5664196882009627</v>
+        <v>1.4952126925398339</v>
       </c>
       <c r="H27" s="0">
-        <v>20.316419688200963</v>
+        <v>20.245212692539834</v>
       </c>
       <c r="I27" s="0">
-        <v>1.0664196882009627</v>
+        <v>0.99521269253983391</v>
       </c>
       <c r="J27" s="0">
-        <v>1.0664196882009627</v>
+        <v>0.99521269253983391</v>
       </c>
       <c r="K27" s="0" t="b">
         <v>1</v>
@@ -1634,28 +1634,28 @@
         <v>69</v>
       </c>
       <c r="C28" s="0">
-        <v>684.71199999999999</v>
+        <v>679.27729999999997</v>
       </c>
       <c r="D28" s="0">
         <v>21.75</v>
       </c>
       <c r="E28" s="0">
-        <v>21.581799004931987</v>
+        <v>21.353576303693472</v>
       </c>
       <c r="F28" s="0">
-        <v>-0.16820099506801256</v>
+        <v>-0.39642369630652752</v>
       </c>
       <c r="G28" s="0">
-        <v>0.16820099506801256</v>
+        <v>0.39642369630652752</v>
       </c>
       <c r="H28" s="0">
-        <v>21.081799004931987</v>
+        <v>20.853576303693472</v>
       </c>
       <c r="I28" s="0">
-        <v>-0.66820099506801256</v>
+        <v>-0.89642369630652752</v>
       </c>
       <c r="J28" s="0">
-        <v>0.66820099506801256</v>
+        <v>0.89642369630652752</v>
       </c>
       <c r="K28" s="0" t="b">
         <v>0</v>
@@ -1678,28 +1678,28 @@
         <v>69</v>
       </c>
       <c r="C29" s="0">
-        <v>527.95719999999994</v>
+        <v>531.55600000000004</v>
       </c>
       <c r="D29" s="0">
         <v>20.75</v>
       </c>
       <c r="E29" s="0">
-        <v>19.054132672820721</v>
+        <v>19.082204937297267</v>
       </c>
       <c r="F29" s="0">
-        <v>-1.695867327179279</v>
+        <v>-1.6677950627027336</v>
       </c>
       <c r="G29" s="0">
-        <v>1.695867327179279</v>
+        <v>1.6677950627027336</v>
       </c>
       <c r="H29" s="0">
-        <v>18.554132672820721</v>
+        <v>18.582204937297267</v>
       </c>
       <c r="I29" s="0">
-        <v>-2.195867327179279</v>
+        <v>-2.1677950627027336</v>
       </c>
       <c r="J29" s="0">
-        <v>2.195867327179279</v>
+        <v>2.1677950627027336</v>
       </c>
       <c r="K29" s="0" t="b">
         <v>0</v>
@@ -1722,28 +1722,28 @@
         <v>69</v>
       </c>
       <c r="C30" s="0">
-        <v>683.46259999999995</v>
+        <v>685.61059999999998</v>
       </c>
       <c r="D30" s="0">
         <v>21.5</v>
       </c>
       <c r="E30" s="0">
-        <v>21.803907792554881</v>
+        <v>21.778330030685631</v>
       </c>
       <c r="F30" s="0">
-        <v>0.30390779255488098</v>
+        <v>0.27833003068563045</v>
       </c>
       <c r="G30" s="0">
-        <v>0.30390779255488098</v>
+        <v>0.27833003068563045</v>
       </c>
       <c r="H30" s="0">
-        <v>21.303907792554881</v>
+        <v>21.278330030685631</v>
       </c>
       <c r="I30" s="0">
-        <v>-0.19609220744511902</v>
+        <v>-0.22166996931436955</v>
       </c>
       <c r="J30" s="0">
-        <v>0.19609220744511902</v>
+        <v>0.22166996931436955</v>
       </c>
       <c r="K30" s="0" t="b">
         <v>0</v>
@@ -1766,28 +1766,28 @@
         <v>69</v>
       </c>
       <c r="C31" s="0">
-        <v>678.49210000000005</v>
+        <v>683.32539999999995</v>
       </c>
       <c r="D31" s="0">
         <v>19.5</v>
       </c>
       <c r="E31" s="0">
-        <v>21.98485886192659</v>
+        <v>22.014228302164447</v>
       </c>
       <c r="F31" s="0">
-        <v>2.4848588619265897</v>
+        <v>2.5142283021644474</v>
       </c>
       <c r="G31" s="0">
-        <v>2.4848588619265897</v>
+        <v>2.5142283021644474</v>
       </c>
       <c r="H31" s="0">
-        <v>21.48485886192659</v>
+        <v>21.514228302164447</v>
       </c>
       <c r="I31" s="0">
-        <v>1.9848588619265897</v>
+        <v>2.0142283021644474</v>
       </c>
       <c r="J31" s="0">
-        <v>1.9848588619265897</v>
+        <v>2.0142283021644474</v>
       </c>
       <c r="K31" s="0" t="b">
         <v>1</v>
@@ -1810,28 +1810,28 @@
         <v>69</v>
       </c>
       <c r="C32" s="0">
-        <v>656.11270000000002</v>
+        <v>669.30840000000001</v>
       </c>
       <c r="D32" s="0">
         <v>19.5</v>
       </c>
       <c r="E32" s="0">
-        <v>21.453616619147326</v>
+        <v>21.659225758580952</v>
       </c>
       <c r="F32" s="0">
-        <v>1.9536166191473257</v>
+        <v>2.159225758580952</v>
       </c>
       <c r="G32" s="0">
-        <v>1.9536166191473257</v>
+        <v>2.159225758580952</v>
       </c>
       <c r="H32" s="0">
-        <v>20.953616619147326</v>
+        <v>21.159225758580952</v>
       </c>
       <c r="I32" s="0">
-        <v>1.4536166191473257</v>
+        <v>1.659225758580952</v>
       </c>
       <c r="J32" s="0">
-        <v>1.4536166191473257</v>
+        <v>1.659225758580952</v>
       </c>
       <c r="K32" s="0" t="b">
         <v>1</v>
@@ -1854,31 +1854,31 @@
         <v>69</v>
       </c>
       <c r="C33" s="0">
-        <v>679.53120000000001</v>
+        <v>712.56219999999996</v>
       </c>
       <c r="D33" s="0">
         <v>21</v>
       </c>
       <c r="E33" s="0">
-        <v>21.145735573716575</v>
+        <v>21.758997338582411</v>
       </c>
       <c r="F33" s="0">
-        <v>0.14573557371657486</v>
+        <v>0.75899733858241092</v>
       </c>
       <c r="G33" s="0">
-        <v>0.14573557371657486</v>
+        <v>0.75899733858241092</v>
       </c>
       <c r="H33" s="0">
-        <v>20.645735573716575</v>
+        <v>21.258997338582411</v>
       </c>
       <c r="I33" s="0">
-        <v>-0.35426442628342514</v>
+        <v>0.25899733858241092</v>
       </c>
       <c r="J33" s="0">
-        <v>0.35426442628342514</v>
+        <v>0.25899733858241092</v>
       </c>
       <c r="K33" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="0">
         <v>1</v>
@@ -1898,28 +1898,28 @@
         <v>69</v>
       </c>
       <c r="C34" s="0">
-        <v>611.02089999999998</v>
+        <v>611.39670000000001</v>
       </c>
       <c r="D34" s="0">
         <v>20.25</v>
       </c>
       <c r="E34" s="0">
-        <v>20.386899987997889</v>
+        <v>20.566635624560245</v>
       </c>
       <c r="F34" s="0">
-        <v>0.13689998799788938</v>
+        <v>0.31663562456024508</v>
       </c>
       <c r="G34" s="0">
-        <v>0.13689998799788938</v>
+        <v>0.31663562456024508</v>
       </c>
       <c r="H34" s="0">
-        <v>19.886899987997889</v>
+        <v>20.066635624560245</v>
       </c>
       <c r="I34" s="0">
-        <v>-0.36310001200211062</v>
+        <v>-0.18336437543975492</v>
       </c>
       <c r="J34" s="0">
-        <v>0.36310001200211062</v>
+        <v>0.18336437543975492</v>
       </c>
       <c r="K34" s="0" t="b">
         <v>0</v>
@@ -1942,28 +1942,28 @@
         <v>69</v>
       </c>
       <c r="C35" s="0">
-        <v>623.09130000000005</v>
+        <v>622.68050000000005</v>
       </c>
       <c r="D35" s="0">
         <v>21.5</v>
       </c>
       <c r="E35" s="0">
-        <v>20.480884320487736</v>
+        <v>20.455945580110026</v>
       </c>
       <c r="F35" s="0">
-        <v>-1.0191156795122645</v>
+        <v>-1.0440544198899744</v>
       </c>
       <c r="G35" s="0">
-        <v>1.0191156795122645</v>
+        <v>1.0440544198899744</v>
       </c>
       <c r="H35" s="0">
-        <v>19.980884320487736</v>
+        <v>19.955945580110026</v>
       </c>
       <c r="I35" s="0">
-        <v>-1.5191156795122644</v>
+        <v>-1.5440544198899744</v>
       </c>
       <c r="J35" s="0">
-        <v>1.5191156795122644</v>
+        <v>1.5440544198899744</v>
       </c>
       <c r="K35" s="0" t="b">
         <v>0</v>
@@ -1986,28 +1986,28 @@
         <v>69</v>
       </c>
       <c r="C36" s="0">
-        <v>590.04459999999995</v>
+        <v>601.95100000000002</v>
       </c>
       <c r="D36" s="0">
         <v>19.5</v>
       </c>
       <c r="E36" s="0">
-        <v>20.02902402576434</v>
+        <v>20.166826730832764</v>
       </c>
       <c r="F36" s="0">
-        <v>0.52902402576433971</v>
+        <v>0.66682673083276356</v>
       </c>
       <c r="G36" s="0">
-        <v>0.52902402576433971</v>
+        <v>0.66682673083276356</v>
       </c>
       <c r="H36" s="0">
-        <v>19.52902402576434</v>
+        <v>19.666826730832764</v>
       </c>
       <c r="I36" s="0">
-        <v>0.029024025764339712</v>
+        <v>0.16682673083276356</v>
       </c>
       <c r="J36" s="0">
-        <v>0.029024025764339712</v>
+        <v>0.16682673083276356</v>
       </c>
       <c r="K36" s="0" t="b">
         <v>1</v>
@@ -2030,28 +2030,28 @@
         <v>69</v>
       </c>
       <c r="C37" s="0">
-        <v>724.99620000000004</v>
+        <v>726.80799999999999</v>
       </c>
       <c r="D37" s="0">
         <v>25</v>
       </c>
       <c r="E37" s="0">
-        <v>22.484131946838033</v>
+        <v>22.5148311612624</v>
       </c>
       <c r="F37" s="0">
-        <v>-2.5158680531619666</v>
+        <v>-2.4851688387376001</v>
       </c>
       <c r="G37" s="0">
-        <v>2.5158680531619666</v>
+        <v>2.4851688387376001</v>
       </c>
       <c r="H37" s="0">
-        <v>21.984131946838033</v>
+        <v>22.0148311612624</v>
       </c>
       <c r="I37" s="0">
-        <v>-3.0158680531619666</v>
+        <v>-2.9851688387376001</v>
       </c>
       <c r="J37" s="0">
-        <v>3.0158680531619666</v>
+        <v>2.9851688387376001</v>
       </c>
       <c r="K37" s="0" t="b">
         <v>0</v>
@@ -2074,28 +2074,28 @@
         <v>69</v>
       </c>
       <c r="C38" s="0">
-        <v>600.44100000000003</v>
+        <v>599.73789999999997</v>
       </c>
       <c r="D38" s="0">
         <v>19</v>
       </c>
       <c r="E38" s="0">
-        <v>19.92853417854835</v>
+        <v>19.896838493016269</v>
       </c>
       <c r="F38" s="0">
-        <v>0.9285341785483503</v>
+        <v>0.8968384930162685</v>
       </c>
       <c r="G38" s="0">
-        <v>0.9285341785483503</v>
+        <v>0.8968384930162685</v>
       </c>
       <c r="H38" s="0">
-        <v>19.42853417854835</v>
+        <v>19.396838493016269</v>
       </c>
       <c r="I38" s="0">
-        <v>0.4285341785483503</v>
+        <v>0.3968384930162685</v>
       </c>
       <c r="J38" s="0">
-        <v>0.4285341785483503</v>
+        <v>0.3968384930162685</v>
       </c>
       <c r="K38" s="0" t="b">
         <v>1</v>
@@ -2118,28 +2118,28 @@
         <v>69</v>
       </c>
       <c r="C39" s="0">
-        <v>692.81489999999997</v>
+        <v>700.04589999999996</v>
       </c>
       <c r="D39" s="0">
         <v>19</v>
       </c>
       <c r="E39" s="0">
-        <v>20.333703584284368</v>
+        <v>20.109725143532462</v>
       </c>
       <c r="F39" s="0">
-        <v>1.3337035842843683</v>
+        <v>1.1097251435324616</v>
       </c>
       <c r="G39" s="0">
-        <v>1.3337035842843683</v>
+        <v>1.1097251435324616</v>
       </c>
       <c r="H39" s="0">
-        <v>19.833703584284368</v>
+        <v>19.609725143532462</v>
       </c>
       <c r="I39" s="0">
-        <v>0.8337035842843683</v>
+        <v>0.60972514353246155</v>
       </c>
       <c r="J39" s="0">
-        <v>0.8337035842843683</v>
+        <v>0.60972514353246155</v>
       </c>
       <c r="K39" s="0" t="b">
         <v>1</v>
@@ -2162,28 +2162,28 @@
         <v>69</v>
       </c>
       <c r="C40" s="0">
-        <v>777.77840000000003</v>
+        <v>776.98199999999997</v>
       </c>
       <c r="D40" s="0">
         <v>21</v>
       </c>
       <c r="E40" s="0">
-        <v>23.63518910271199</v>
+        <v>23.748642067456501</v>
       </c>
       <c r="F40" s="0">
-        <v>2.6351891027119905</v>
+        <v>2.7486420674565011</v>
       </c>
       <c r="G40" s="0">
-        <v>2.6351891027119905</v>
+        <v>2.7486420674565011</v>
       </c>
       <c r="H40" s="0">
-        <v>23.13518910271199</v>
+        <v>23.248642067456501</v>
       </c>
       <c r="I40" s="0">
-        <v>2.1351891027119905</v>
+        <v>2.2486420674565011</v>
       </c>
       <c r="J40" s="0">
-        <v>2.1351891027119905</v>
+        <v>2.2486420674565011</v>
       </c>
       <c r="K40" s="0" t="b">
         <v>1</v>
@@ -2206,28 +2206,28 @@
         <v>69</v>
       </c>
       <c r="C41" s="0">
-        <v>666.36320000000001</v>
+        <v>673.32410000000004</v>
       </c>
       <c r="D41" s="0">
         <v>20.5</v>
       </c>
       <c r="E41" s="0">
-        <v>21.273293382822999</v>
+        <v>21.351311293723949</v>
       </c>
       <c r="F41" s="0">
-        <v>0.77329338282299887</v>
+        <v>0.85131129372394909</v>
       </c>
       <c r="G41" s="0">
-        <v>0.77329338282299887</v>
+        <v>0.85131129372394909</v>
       </c>
       <c r="H41" s="0">
-        <v>20.773293382822999</v>
+        <v>20.851311293723949</v>
       </c>
       <c r="I41" s="0">
-        <v>0.27329338282299887</v>
+        <v>0.35131129372394909</v>
       </c>
       <c r="J41" s="0">
-        <v>0.27329338282299887</v>
+        <v>0.35131129372394909</v>
       </c>
       <c r="K41" s="0" t="b">
         <v>1</v>
@@ -2250,28 +2250,28 @@
         <v>69</v>
       </c>
       <c r="C42" s="0">
-        <v>518.52380000000005</v>
+        <v>526.36469999999997</v>
       </c>
       <c r="D42" s="0">
         <v>19.25</v>
       </c>
       <c r="E42" s="0">
-        <v>19.112717481611767</v>
+        <v>19.12980026837257</v>
       </c>
       <c r="F42" s="0">
-        <v>-0.13728251838823269</v>
+        <v>-0.12019973162743014</v>
       </c>
       <c r="G42" s="0">
-        <v>0.13728251838823269</v>
+        <v>0.12019973162743014</v>
       </c>
       <c r="H42" s="0">
-        <v>18.612717481611767</v>
+        <v>18.62980026837257</v>
       </c>
       <c r="I42" s="0">
-        <v>-0.63728251838823269</v>
+        <v>-0.62019973162743014</v>
       </c>
       <c r="J42" s="0">
-        <v>0.63728251838823269</v>
+        <v>0.62019973162743014</v>
       </c>
       <c r="K42" s="0" t="b">
         <v>0</v>
@@ -2294,28 +2294,28 @@
         <v>69</v>
       </c>
       <c r="C43" s="0">
-        <v>582.97400000000005</v>
+        <v>586.85530000000006</v>
       </c>
       <c r="D43" s="0">
         <v>20</v>
       </c>
       <c r="E43" s="0">
-        <v>19.579888228190452</v>
+        <v>19.600739334387431</v>
       </c>
       <c r="F43" s="0">
-        <v>-0.42011177180954817</v>
+        <v>-0.39926066561256946</v>
       </c>
       <c r="G43" s="0">
-        <v>0.42011177180954817</v>
+        <v>0.39926066561256946</v>
       </c>
       <c r="H43" s="0">
-        <v>19.079888228190452</v>
+        <v>19.100739334387431</v>
       </c>
       <c r="I43" s="0">
-        <v>-0.92011177180954817</v>
+        <v>-0.89926066561256946</v>
       </c>
       <c r="J43" s="0">
-        <v>0.92011177180954817</v>
+        <v>0.89926066561256946</v>
       </c>
       <c r="K43" s="0" t="b">
         <v>0</v>
@@ -2338,28 +2338,28 @@
         <v>69</v>
       </c>
       <c r="C44" s="0">
-        <v>657.05769999999996</v>
+        <v>663.21749999999997</v>
       </c>
       <c r="D44" s="0">
         <v>20</v>
       </c>
       <c r="E44" s="0">
-        <v>20.994095783542726</v>
+        <v>21.130369959153626</v>
       </c>
       <c r="F44" s="0">
-        <v>0.99409578354272554</v>
+        <v>1.1303699591536258</v>
       </c>
       <c r="G44" s="0">
-        <v>0.99409578354272554</v>
+        <v>1.1303699591536258</v>
       </c>
       <c r="H44" s="0">
-        <v>20.494095783542726</v>
+        <v>20.630369959153626</v>
       </c>
       <c r="I44" s="0">
-        <v>0.49409578354272554</v>
+        <v>0.63036995915362581</v>
       </c>
       <c r="J44" s="0">
-        <v>0.49409578354272554</v>
+        <v>0.63036995915362581</v>
       </c>
       <c r="K44" s="0" t="b">
         <v>1</v>
@@ -2382,28 +2382,28 @@
         <v>69</v>
       </c>
       <c r="C45" s="0">
-        <v>584.81910000000005</v>
+        <v>582.90459999999996</v>
       </c>
       <c r="D45" s="0">
         <v>20</v>
       </c>
       <c r="E45" s="0">
-        <v>19.991671360135403</v>
+        <v>19.963563699796481</v>
       </c>
       <c r="F45" s="0">
-        <v>-0.0083286398645974202</v>
+        <v>-0.036436300203519068</v>
       </c>
       <c r="G45" s="0">
-        <v>0.0083286398645974202</v>
+        <v>0.036436300203519068</v>
       </c>
       <c r="H45" s="0">
-        <v>19.491671360135403</v>
+        <v>19.463563699796481</v>
       </c>
       <c r="I45" s="0">
-        <v>-0.50832863986459742</v>
+        <v>-0.53643630020351907</v>
       </c>
       <c r="J45" s="0">
-        <v>0.50832863986459742</v>
+        <v>0.53643630020351907</v>
       </c>
       <c r="K45" s="0" t="b">
         <v>0</v>
@@ -2426,28 +2426,28 @@
         <v>69</v>
       </c>
       <c r="C46" s="0">
-        <v>728.66980000000001</v>
+        <v>732.64890000000003</v>
       </c>
       <c r="D46" s="0">
         <v>22</v>
       </c>
       <c r="E46" s="0">
-        <v>24.26050166516799</v>
+        <v>24.299107014904109</v>
       </c>
       <c r="F46" s="0">
-        <v>2.2605016651679897</v>
+        <v>2.2991070149041093</v>
       </c>
       <c r="G46" s="0">
-        <v>2.2605016651679897</v>
+        <v>2.2991070149041093</v>
       </c>
       <c r="H46" s="0">
-        <v>23.76050166516799</v>
+        <v>23.799107014904109</v>
       </c>
       <c r="I46" s="0">
-        <v>1.7605016651679897</v>
+        <v>1.7991070149041093</v>
       </c>
       <c r="J46" s="0">
-        <v>1.7605016651679897</v>
+        <v>1.7991070149041093</v>
       </c>
       <c r="K46" s="0" t="b">
         <v>1</v>
@@ -2470,28 +2470,28 @@
         <v>69</v>
       </c>
       <c r="C47" s="0">
-        <v>697.34799999999996</v>
+        <v>704.21619999999996</v>
       </c>
       <c r="D47" s="0">
         <v>22</v>
       </c>
       <c r="E47" s="0">
-        <v>22.743330950841873</v>
+        <v>22.735432536726279</v>
       </c>
       <c r="F47" s="0">
-        <v>0.74333095084187306</v>
+        <v>0.73543253672627884</v>
       </c>
       <c r="G47" s="0">
-        <v>0.74333095084187306</v>
+        <v>0.73543253672627884</v>
       </c>
       <c r="H47" s="0">
-        <v>22.243330950841873</v>
+        <v>22.235432536726279</v>
       </c>
       <c r="I47" s="0">
-        <v>0.24333095084187306</v>
+        <v>0.23543253672627884</v>
       </c>
       <c r="J47" s="0">
-        <v>0.24333095084187306</v>
+        <v>0.23543253672627884</v>
       </c>
       <c r="K47" s="0" t="b">
         <v>1</v>
@@ -2514,28 +2514,28 @@
         <v>69</v>
       </c>
       <c r="C48" s="0">
-        <v>696.77610000000004</v>
+        <v>707.67989999999998</v>
       </c>
       <c r="D48" s="0">
         <v>23</v>
       </c>
       <c r="E48" s="0">
-        <v>21.852127979078457</v>
+        <v>22.070499914635604</v>
       </c>
       <c r="F48" s="0">
-        <v>-1.1478720209215432</v>
+        <v>-0.92950008536439555</v>
       </c>
       <c r="G48" s="0">
-        <v>1.1478720209215432</v>
+        <v>0.92950008536439555</v>
       </c>
       <c r="H48" s="0">
-        <v>21.352127979078457</v>
+        <v>21.570499914635604</v>
       </c>
       <c r="I48" s="0">
-        <v>-1.6478720209215432</v>
+        <v>-1.4295000853643955</v>
       </c>
       <c r="J48" s="0">
-        <v>1.6478720209215432</v>
+        <v>1.4295000853643955</v>
       </c>
       <c r="K48" s="0" t="b">
         <v>0</v>
@@ -2558,28 +2558,28 @@
         <v>69</v>
       </c>
       <c r="C49" s="0">
-        <v>664.47260000000006</v>
+        <v>666.81700000000001</v>
       </c>
       <c r="D49" s="0">
         <v>21.75</v>
       </c>
       <c r="E49" s="0">
-        <v>21.086149670525167</v>
+        <v>21.101204944293261</v>
       </c>
       <c r="F49" s="0">
-        <v>-0.66385032947483325</v>
+        <v>-0.64879505570673857</v>
       </c>
       <c r="G49" s="0">
-        <v>0.66385032947483325</v>
+        <v>0.64879505570673857</v>
       </c>
       <c r="H49" s="0">
-        <v>20.586149670525167</v>
+        <v>20.601204944293261</v>
       </c>
       <c r="I49" s="0">
-        <v>-1.1638503294748333</v>
+        <v>-1.1487950557067386</v>
       </c>
       <c r="J49" s="0">
-        <v>1.1638503294748333</v>
+        <v>1.1487950557067386</v>
       </c>
       <c r="K49" s="0" t="b">
         <v>0</v>
@@ -2602,28 +2602,28 @@
         <v>69</v>
       </c>
       <c r="C50" s="0">
-        <v>686.67639999999995</v>
+        <v>688.77390000000003</v>
       </c>
       <c r="D50" s="0">
         <v>21.5</v>
       </c>
       <c r="E50" s="0">
-        <v>21.61907706581033</v>
+        <v>21.564966619938438</v>
       </c>
       <c r="F50" s="0">
-        <v>0.1190770658103304</v>
+        <v>0.064966619938438441</v>
       </c>
       <c r="G50" s="0">
-        <v>0.1190770658103304</v>
+        <v>0.064966619938438441</v>
       </c>
       <c r="H50" s="0">
-        <v>21.11907706581033</v>
+        <v>21.064966619938438</v>
       </c>
       <c r="I50" s="0">
-        <v>-0.38092293418966961</v>
+        <v>-0.43503338006156156</v>
       </c>
       <c r="J50" s="0">
-        <v>0.38092293418966961</v>
+        <v>0.43503338006156156</v>
       </c>
       <c r="K50" s="0" t="b">
         <v>0</v>
@@ -2646,28 +2646,28 @@
         <v>69</v>
       </c>
       <c r="C51" s="0">
-        <v>616.17359999999997</v>
+        <v>615.82560000000001</v>
       </c>
       <c r="D51" s="0">
         <v>19.199999999999999</v>
       </c>
       <c r="E51" s="0">
-        <v>20.383166413930809</v>
+        <v>20.297450716701004</v>
       </c>
       <c r="F51" s="0">
-        <v>1.1831664139308096</v>
+        <v>1.0974507167010046</v>
       </c>
       <c r="G51" s="0">
-        <v>1.1831664139308096</v>
+        <v>1.0974507167010046</v>
       </c>
       <c r="H51" s="0">
-        <v>19.883166413930809</v>
+        <v>19.797450716701004</v>
       </c>
       <c r="I51" s="0">
-        <v>0.68316641393080957</v>
+        <v>0.59745071670100458</v>
       </c>
       <c r="J51" s="0">
-        <v>0.68316641393080957</v>
+        <v>0.59745071670100458</v>
       </c>
       <c r="K51" s="0" t="b">
         <v>1</v>
@@ -2690,28 +2690,28 @@
         <v>69</v>
       </c>
       <c r="C52" s="0">
-        <v>575.9733</v>
+        <v>568.91740000000004</v>
       </c>
       <c r="D52" s="0">
         <v>17.5</v>
       </c>
       <c r="E52" s="0">
-        <v>19.810425805715763</v>
+        <v>19.738454519574312</v>
       </c>
       <c r="F52" s="0">
-        <v>2.3104258057157629</v>
+        <v>2.2384545195743115</v>
       </c>
       <c r="G52" s="0">
-        <v>2.3104258057157629</v>
+        <v>2.2384545195743115</v>
       </c>
       <c r="H52" s="0">
-        <v>19.310425805715763</v>
+        <v>19.238454519574312</v>
       </c>
       <c r="I52" s="0">
-        <v>1.8104258057157629</v>
+        <v>1.7384545195743115</v>
       </c>
       <c r="J52" s="0">
-        <v>1.8104258057157629</v>
+        <v>1.7384545195743115</v>
       </c>
       <c r="K52" s="0" t="b">
         <v>1</v>
@@ -2734,28 +2734,28 @@
         <v>69</v>
       </c>
       <c r="C53" s="0">
-        <v>589.5335</v>
+        <v>594.03499999999997</v>
       </c>
       <c r="D53" s="0">
         <v>18.399999999999999</v>
       </c>
       <c r="E53" s="0">
-        <v>19.939860396814776</v>
+        <v>19.920713124577375</v>
       </c>
       <c r="F53" s="0">
-        <v>1.5398603968147775</v>
+        <v>1.5207131245773766</v>
       </c>
       <c r="G53" s="0">
-        <v>1.5398603968147775</v>
+        <v>1.5207131245773766</v>
       </c>
       <c r="H53" s="0">
-        <v>19.439860396814776</v>
+        <v>19.420713124577375</v>
       </c>
       <c r="I53" s="0">
-        <v>1.0398603968147775</v>
+        <v>1.0207131245773766</v>
       </c>
       <c r="J53" s="0">
-        <v>1.0398603968147775</v>
+        <v>1.0207131245773766</v>
       </c>
       <c r="K53" s="0" t="b">
         <v>1</v>
@@ -2778,28 +2778,28 @@
         <v>69</v>
       </c>
       <c r="C54" s="0">
-        <v>563.72389999999996</v>
+        <v>566.51940000000002</v>
       </c>
       <c r="D54" s="0">
         <v>19</v>
       </c>
       <c r="E54" s="0">
-        <v>19.509614475153679</v>
+        <v>19.532823848349199</v>
       </c>
       <c r="F54" s="0">
-        <v>0.50961447515367908</v>
+        <v>0.53282384834919938</v>
       </c>
       <c r="G54" s="0">
-        <v>0.50961447515367908</v>
+        <v>0.53282384834919938</v>
       </c>
       <c r="H54" s="0">
-        <v>19.009614475153679</v>
+        <v>19.032823848349199</v>
       </c>
       <c r="I54" s="0">
-        <v>0.0096144751536790807</v>
+        <v>0.03282384834919938</v>
       </c>
       <c r="J54" s="0">
-        <v>0.0096144751536790807</v>
+        <v>0.03282384834919938</v>
       </c>
       <c r="K54" s="0" t="b">
         <v>1</v>
@@ -2822,28 +2822,28 @@
         <v>69</v>
       </c>
       <c r="C55" s="0">
-        <v>600.82780000000002</v>
+        <v>614.26739999999995</v>
       </c>
       <c r="D55" s="0">
         <v>19.5</v>
       </c>
       <c r="E55" s="0">
-        <v>20.061926393129106</v>
+        <v>20.252026655178678</v>
       </c>
       <c r="F55" s="0">
-        <v>0.56192639312910586</v>
+        <v>0.75202665517867828</v>
       </c>
       <c r="G55" s="0">
-        <v>0.56192639312910586</v>
+        <v>0.75202665517867828</v>
       </c>
       <c r="H55" s="0">
-        <v>19.561926393129106</v>
+        <v>19.752026655178678</v>
       </c>
       <c r="I55" s="0">
-        <v>0.061926393129105861</v>
+        <v>0.25202665517867828</v>
       </c>
       <c r="J55" s="0">
-        <v>0.061926393129105861</v>
+        <v>0.25202665517867828</v>
       </c>
       <c r="K55" s="0" t="b">
         <v>1</v>
@@ -2866,28 +2866,28 @@
         <v>69</v>
       </c>
       <c r="C56" s="0">
-        <v>727.90769999999998</v>
+        <v>717.47789999999998</v>
       </c>
       <c r="D56" s="0">
         <v>20.5</v>
       </c>
       <c r="E56" s="0">
-        <v>23.103270641751948</v>
+        <v>22.501810412115908</v>
       </c>
       <c r="F56" s="0">
-        <v>2.6032706417519478</v>
+        <v>2.0018104121159084</v>
       </c>
       <c r="G56" s="0">
-        <v>2.6032706417519478</v>
+        <v>2.0018104121159084</v>
       </c>
       <c r="H56" s="0">
-        <v>22.603270641751948</v>
+        <v>22.001810412115908</v>
       </c>
       <c r="I56" s="0">
-        <v>2.1032706417519478</v>
+        <v>1.5018104121159084</v>
       </c>
       <c r="J56" s="0">
-        <v>2.1032706417519478</v>
+        <v>1.5018104121159084</v>
       </c>
       <c r="K56" s="0" t="b">
         <v>1</v>
@@ -2910,28 +2910,28 @@
         <v>69</v>
       </c>
       <c r="C57" s="0">
-        <v>646.02480000000003</v>
+        <v>656.12369999999999</v>
       </c>
       <c r="D57" s="0">
         <v>21</v>
       </c>
       <c r="E57" s="0">
-        <v>20.690614310751119</v>
+        <v>20.830567540357542</v>
       </c>
       <c r="F57" s="0">
-        <v>-0.30938568924888088</v>
+        <v>-0.1694324596424579</v>
       </c>
       <c r="G57" s="0">
-        <v>0.30938568924888088</v>
+        <v>0.1694324596424579</v>
       </c>
       <c r="H57" s="0">
-        <v>20.190614310751119</v>
+        <v>20.330567540357542</v>
       </c>
       <c r="I57" s="0">
-        <v>-0.80938568924888088</v>
+        <v>-0.6694324596424579</v>
       </c>
       <c r="J57" s="0">
-        <v>0.80938568924888088</v>
+        <v>0.6694324596424579</v>
       </c>
       <c r="K57" s="0" t="b">
         <v>0</v>
@@ -2954,28 +2954,28 @@
         <v>69</v>
       </c>
       <c r="C58" s="0">
-        <v>730.19860000000006</v>
+        <v>713.17060000000004</v>
       </c>
       <c r="D58" s="0">
         <v>23.5</v>
       </c>
       <c r="E58" s="0">
-        <v>22.322006015899891</v>
+        <v>21.93208406768094</v>
       </c>
       <c r="F58" s="0">
-        <v>-1.1779939841001088</v>
+        <v>-1.5679159323190604</v>
       </c>
       <c r="G58" s="0">
-        <v>1.1779939841001088</v>
+        <v>1.5679159323190604</v>
       </c>
       <c r="H58" s="0">
-        <v>21.822006015899891</v>
+        <v>21.43208406768094</v>
       </c>
       <c r="I58" s="0">
-        <v>-1.6779939841001088</v>
+        <v>-2.0679159323190604</v>
       </c>
       <c r="J58" s="0">
-        <v>1.6779939841001088</v>
+        <v>2.0679159323190604</v>
       </c>
       <c r="K58" s="0" t="b">
         <v>0</v>
@@ -2998,28 +2998,28 @@
         <v>69</v>
       </c>
       <c r="C59" s="0">
-        <v>665.77250000000004</v>
+        <v>675.12120000000004</v>
       </c>
       <c r="D59" s="0">
         <v>20.5</v>
       </c>
       <c r="E59" s="0">
-        <v>21.161356172674157</v>
+        <v>21.296960252043835</v>
       </c>
       <c r="F59" s="0">
-        <v>0.66135617267415725</v>
+        <v>0.79696025204383503</v>
       </c>
       <c r="G59" s="0">
-        <v>0.66135617267415725</v>
+        <v>0.79696025204383503</v>
       </c>
       <c r="H59" s="0">
-        <v>20.661356172674157</v>
+        <v>20.796960252043835</v>
       </c>
       <c r="I59" s="0">
-        <v>0.16135617267415725</v>
+        <v>0.29696025204383503</v>
       </c>
       <c r="J59" s="0">
-        <v>0.16135617267415725</v>
+        <v>0.29696025204383503</v>
       </c>
       <c r="K59" s="0" t="b">
         <v>1</v>
@@ -3042,28 +3042,28 @@
         <v>69</v>
       </c>
       <c r="C60" s="0">
-        <v>695.50199999999995</v>
+        <v>689.68129999999997</v>
       </c>
       <c r="D60" s="0">
         <v>21.5</v>
       </c>
       <c r="E60" s="0">
-        <v>21.658210199658747</v>
+        <v>21.400137657767285</v>
       </c>
       <c r="F60" s="0">
-        <v>0.15821019965874683</v>
+        <v>-0.099862342232714951</v>
       </c>
       <c r="G60" s="0">
-        <v>0.15821019965874683</v>
+        <v>0.099862342232714951</v>
       </c>
       <c r="H60" s="0">
-        <v>21.158210199658747</v>
+        <v>20.900137657767285</v>
       </c>
       <c r="I60" s="0">
-        <v>-0.34178980034125317</v>
+        <v>-0.59986234223271495</v>
       </c>
       <c r="J60" s="0">
-        <v>0.34178980034125317</v>
+        <v>0.59986234223271495</v>
       </c>
       <c r="K60" s="0" t="b">
         <v>0</v>
@@ -3086,31 +3086,31 @@
         <v>69</v>
       </c>
       <c r="C61" s="0">
-        <v>639.4633</v>
+        <v>646.9873</v>
       </c>
       <c r="D61" s="0">
         <v>20</v>
       </c>
       <c r="E61" s="0">
-        <v>20.470429037437864</v>
+        <v>20.500889305829464</v>
       </c>
       <c r="F61" s="0">
-        <v>0.47042903743786368</v>
+        <v>0.50088930582946389</v>
       </c>
       <c r="G61" s="0">
-        <v>0.47042903743786368</v>
+        <v>0.50088930582946389</v>
       </c>
       <c r="H61" s="0">
-        <v>19.970429037437864</v>
+        <v>20.000889305829464</v>
       </c>
       <c r="I61" s="0">
-        <v>-0.029570962562136316</v>
+        <v>0.00088930582946389336</v>
       </c>
       <c r="J61" s="0">
-        <v>0.029570962562136316</v>
+        <v>0.00088930582946389336</v>
       </c>
       <c r="K61" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="0">
         <v>4</v>
@@ -3130,28 +3130,28 @@
         <v>69</v>
       </c>
       <c r="C62" s="0">
-        <v>699.43420000000003</v>
+        <v>680.14350000000002</v>
       </c>
       <c r="D62" s="0">
         <v>23</v>
       </c>
       <c r="E62" s="0">
-        <v>21.574523141913346</v>
+        <v>21.123036057278341</v>
       </c>
       <c r="F62" s="0">
-        <v>-1.4254768580866539</v>
+        <v>-1.8769639427216589</v>
       </c>
       <c r="G62" s="0">
-        <v>1.4254768580866539</v>
+        <v>1.8769639427216589</v>
       </c>
       <c r="H62" s="0">
-        <v>21.074523141913346</v>
+        <v>20.623036057278341</v>
       </c>
       <c r="I62" s="0">
-        <v>-1.9254768580866539</v>
+        <v>-2.3769639427216589</v>
       </c>
       <c r="J62" s="0">
-        <v>1.9254768580866539</v>
+        <v>2.3769639427216589</v>
       </c>
       <c r="K62" s="0" t="b">
         <v>0</v>
@@ -3174,28 +3174,28 @@
         <v>69</v>
       </c>
       <c r="C63" s="0">
-        <v>683.36609999999996</v>
+        <v>675.0444</v>
       </c>
       <c r="D63" s="0">
         <v>21.5</v>
       </c>
       <c r="E63" s="0">
-        <v>21.387224062312391</v>
+        <v>21.235582286319343</v>
       </c>
       <c r="F63" s="0">
-        <v>-0.11277593768760852</v>
+        <v>-0.26441771368065759</v>
       </c>
       <c r="G63" s="0">
-        <v>0.11277593768760852</v>
+        <v>0.26441771368065759</v>
       </c>
       <c r="H63" s="0">
-        <v>20.887224062312391</v>
+        <v>20.735582286319343</v>
       </c>
       <c r="I63" s="0">
-        <v>-0.61277593768760852</v>
+        <v>-0.76441771368065758</v>
       </c>
       <c r="J63" s="0">
-        <v>0.61277593768760852</v>
+        <v>0.76441771368065758</v>
       </c>
       <c r="K63" s="0" t="b">
         <v>0</v>
@@ -3218,28 +3218,28 @@
         <v>69</v>
       </c>
       <c r="C64" s="0">
-        <v>635.10969999999998</v>
+        <v>638.85119999999995</v>
       </c>
       <c r="D64" s="0">
         <v>22.5</v>
       </c>
       <c r="E64" s="0">
-        <v>20.58641530789745</v>
+        <v>20.60403726506501</v>
       </c>
       <c r="F64" s="0">
-        <v>-1.9135846921025497</v>
+        <v>-1.8959627349349901</v>
       </c>
       <c r="G64" s="0">
-        <v>1.9135846921025497</v>
+        <v>1.8959627349349901</v>
       </c>
       <c r="H64" s="0">
-        <v>20.08641530789745</v>
+        <v>20.10403726506501</v>
       </c>
       <c r="I64" s="0">
-        <v>-2.4135846921025497</v>
+        <v>-2.3959627349349901</v>
       </c>
       <c r="J64" s="0">
-        <v>2.4135846921025497</v>
+        <v>2.3959627349349901</v>
       </c>
       <c r="K64" s="0" t="b">
         <v>0</v>
@@ -3262,28 +3262,28 @@
         <v>69</v>
       </c>
       <c r="C65" s="0">
-        <v>594.92830000000004</v>
+        <v>595.31380000000001</v>
       </c>
       <c r="D65" s="0">
         <v>19.25</v>
       </c>
       <c r="E65" s="0">
-        <v>19.786298905298356</v>
+        <v>19.771902609257364</v>
       </c>
       <c r="F65" s="0">
-        <v>0.53629890529835578</v>
+        <v>0.52190260925736354</v>
       </c>
       <c r="G65" s="0">
-        <v>0.53629890529835578</v>
+        <v>0.52190260925736354</v>
       </c>
       <c r="H65" s="0">
-        <v>19.286298905298356</v>
+        <v>19.271902609257364</v>
       </c>
       <c r="I65" s="0">
-        <v>0.036298905298355777</v>
+        <v>0.021902609257363537</v>
       </c>
       <c r="J65" s="0">
-        <v>0.036298905298355777</v>
+        <v>0.021902609257363537</v>
       </c>
       <c r="K65" s="0" t="b">
         <v>1</v>
@@ -3306,28 +3306,28 @@
         <v>69</v>
       </c>
       <c r="C66" s="0">
-        <v>672.91949999999997</v>
+        <v>698.0498</v>
       </c>
       <c r="D66" s="0">
         <v>23.5</v>
       </c>
       <c r="E66" s="0">
-        <v>21.257119312677187</v>
+        <v>21.731312678014401</v>
       </c>
       <c r="F66" s="0">
-        <v>-2.2428806873228133</v>
+        <v>-1.768687321985599</v>
       </c>
       <c r="G66" s="0">
-        <v>2.2428806873228133</v>
+        <v>1.768687321985599</v>
       </c>
       <c r="H66" s="0">
-        <v>20.757119312677187</v>
+        <v>21.231312678014401</v>
       </c>
       <c r="I66" s="0">
-        <v>-2.7428806873228133</v>
+        <v>-2.268687321985599</v>
       </c>
       <c r="J66" s="0">
-        <v>2.7428806873228133</v>
+        <v>2.268687321985599</v>
       </c>
       <c r="K66" s="0" t="b">
         <v>0</v>
@@ -3350,28 +3350,28 @@
         <v>69</v>
       </c>
       <c r="C67" s="0">
-        <v>637.33479999999997</v>
+        <v>634.08339999999998</v>
       </c>
       <c r="D67" s="0">
         <v>21.5</v>
       </c>
       <c r="E67" s="0">
-        <v>20.628253503185899</v>
+        <v>20.552128595616768</v>
       </c>
       <c r="F67" s="0">
-        <v>-0.87174649681410088</v>
+        <v>-0.94787140438323192</v>
       </c>
       <c r="G67" s="0">
-        <v>0.87174649681410088</v>
+        <v>0.94787140438323192</v>
       </c>
       <c r="H67" s="0">
-        <v>20.128253503185899</v>
+        <v>20.052128595616768</v>
       </c>
       <c r="I67" s="0">
-        <v>-1.3717464968141009</v>
+        <v>-1.4478714043832319</v>
       </c>
       <c r="J67" s="0">
-        <v>1.3717464968141009</v>
+        <v>1.4478714043832319</v>
       </c>
       <c r="K67" s="0" t="b">
         <v>0</v>
@@ -3394,28 +3394,28 @@
         <v>69</v>
       </c>
       <c r="C68" s="0">
-        <v>572.66319999999996</v>
+        <v>578.7296</v>
       </c>
       <c r="D68" s="0">
         <v>19</v>
       </c>
       <c r="E68" s="0">
-        <v>19.777091222398187</v>
+        <v>19.833218955635616</v>
       </c>
       <c r="F68" s="0">
-        <v>0.7770912223981874</v>
+        <v>0.83321895563561554</v>
       </c>
       <c r="G68" s="0">
-        <v>0.7770912223981874</v>
+        <v>0.83321895563561554</v>
       </c>
       <c r="H68" s="0">
-        <v>19.277091222398187</v>
+        <v>19.333218955635616</v>
       </c>
       <c r="I68" s="0">
-        <v>0.2770912223981874</v>
+        <v>0.33321895563561554</v>
       </c>
       <c r="J68" s="0">
-        <v>0.2770912223981874</v>
+        <v>0.33321895563561554</v>
       </c>
       <c r="K68" s="0" t="b">
         <v>1</v>
@@ -3476,16 +3476,16 @@
         <v>85</v>
       </c>
       <c r="B2" s="0">
-        <v>1.0860000000000001</v>
+        <v>1.0820000000000001</v>
       </c>
       <c r="C2" s="0">
-        <v>1.369</v>
+        <v>1.355</v>
       </c>
       <c r="D2" s="0">
-        <v>0.41999999999999999</v>
+        <v>0.42899999999999999</v>
       </c>
       <c r="E2" s="0">
-        <v>0.068000000000000005</v>
+        <v>0.060999999999999999</v>
       </c>
       <c r="F2" s="0"/>
       <c r="G2" s="0"/>
@@ -3529,18 +3529,18 @@
         <v>88</v>
       </c>
       <c r="B5" s="0">
-        <v>1.093</v>
+        <v>1.0980000000000001</v>
       </c>
       <c r="C5" s="0"/>
       <c r="D5" s="0"/>
       <c r="E5" s="0">
-        <v>-0.432</v>
+        <v>-0.439</v>
       </c>
       <c r="F5" s="0">
-        <v>56.700000000000003</v>
+        <v>58.200000000000003</v>
       </c>
       <c r="G5" s="0">
-        <v>43.299999999999997</v>
+        <v>44.799999999999997</v>
       </c>
     </row>
     <row r="6">
@@ -3548,16 +3548,16 @@
         <v>89</v>
       </c>
       <c r="B6" s="0">
-        <v>1.081</v>
+        <v>1.0940000000000001</v>
       </c>
       <c r="C6" s="0">
-        <v>1.3759999999999999</v>
+        <v>1.3859999999999999</v>
       </c>
       <c r="D6" s="0">
-        <v>0.40600000000000003</v>
+        <v>0.39700000000000002</v>
       </c>
       <c r="E6" s="0">
-        <v>0.016</v>
+        <v>0.014999999999999999</v>
       </c>
       <c r="F6" s="0"/>
       <c r="G6" s="0"/>
@@ -3567,15 +3567,15 @@
         <v>90</v>
       </c>
       <c r="B7" s="0">
-        <v>1.1279999999999999</v>
+        <v>1.157</v>
       </c>
       <c r="C7" s="0"/>
       <c r="D7" s="0"/>
       <c r="E7" s="0">
-        <v>-0.48399999999999999</v>
+        <v>-0.48499999999999999</v>
       </c>
       <c r="F7" s="0">
-        <v>53.700000000000003</v>
+        <v>55.200000000000003</v>
       </c>
       <c r="G7" s="0">
         <v>38.799999999999997</v>
@@ -3688,13 +3688,13 @@
         <v>112</v>
       </c>
       <c r="B2" s="0">
-        <v>9.8839000000000006</v>
+        <v>9.7510999999999992</v>
       </c>
       <c r="C2" s="0">
-        <v>1.7193000000000001</v>
+        <v>1.7554000000000001</v>
       </c>
       <c r="D2" s="0">
-        <v>5.7489999999999997</v>
+        <v>5.5549999999999997</v>
       </c>
       <c r="E2" s="0">
         <v>0</v>
@@ -3705,13 +3705,13 @@
         <v>113</v>
       </c>
       <c r="B3" s="0">
-        <v>0.017999999999999999</v>
+        <v>0.018200000000000001</v>
       </c>
       <c r="C3" s="0">
-        <v>0.0025000000000000001</v>
+        <v>0.0025999999999999999</v>
       </c>
       <c r="D3" s="0">
-        <v>7.1529999999999996</v>
+        <v>7.077</v>
       </c>
       <c r="E3" s="0">
         <v>0</v>
@@ -3722,16 +3722,16 @@
         <v>114</v>
       </c>
       <c r="B4" s="0">
-        <v>-0.0132</v>
+        <v>-0.013899999999999999</v>
       </c>
       <c r="C4" s="0">
         <v>0.0099000000000000008</v>
       </c>
       <c r="D4" s="0">
-        <v>-1.3440000000000001</v>
+        <v>-1.4079999999999999</v>
       </c>
       <c r="E4" s="0">
-        <v>0.18379999999999999</v>
+        <v>0.16389999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/預測結果與評估指標_kfold_mask幾何_長邊正規化_年齡.xlsx
+++ b/預測結果與評估指標_kfold_mask幾何_長邊正規化_年齡.xlsx
@@ -427,7 +427,7 @@
     <col min="3" max="3" width="13.42578125" customWidth="true"/>
     <col min="4" max="4" width="14.7109375" customWidth="true"/>
     <col min="5" max="5" width="14.7109375" customWidth="true"/>
-    <col min="6" max="6" width="15.42578125" customWidth="true"/>
+    <col min="6" max="6" width="13.7109375" customWidth="true"/>
     <col min="7" max="7" width="14.7109375" customWidth="true"/>
     <col min="8" max="8" width="17" customWidth="true"/>
     <col min="9" max="9" width="20.5703125" customWidth="true"/>
@@ -490,28 +490,28 @@
         <v>69</v>
       </c>
       <c r="C2" s="0">
-        <v>606.4973</v>
+        <v>610.42669999999998</v>
       </c>
       <c r="D2" s="0">
         <v>23</v>
       </c>
       <c r="E2" s="0">
-        <v>20.135660141072528</v>
+        <v>20.117571875522362</v>
       </c>
       <c r="F2" s="0">
-        <v>-2.8643398589274724</v>
+        <v>-2.882428124477638</v>
       </c>
       <c r="G2" s="0">
-        <v>2.8643398589274724</v>
+        <v>2.882428124477638</v>
       </c>
       <c r="H2" s="0">
-        <v>19.635660141072528</v>
+        <v>19.617571875522362</v>
       </c>
       <c r="I2" s="0">
-        <v>-3.3643398589274725</v>
+        <v>-3.382428124477638</v>
       </c>
       <c r="J2" s="0">
-        <v>3.3643398589274725</v>
+        <v>3.382428124477638</v>
       </c>
       <c r="K2" s="0" t="b">
         <v>0</v>
@@ -534,28 +534,28 @@
         <v>69</v>
       </c>
       <c r="C3" s="0">
-        <v>609.20730000000003</v>
+        <v>618.74630000000002</v>
       </c>
       <c r="D3" s="0">
         <v>21</v>
       </c>
       <c r="E3" s="0">
-        <v>20.437494320769254</v>
+        <v>20.464330929728497</v>
       </c>
       <c r="F3" s="0">
-        <v>-0.56250567923074613</v>
+        <v>-0.53566907027150279</v>
       </c>
       <c r="G3" s="0">
-        <v>0.56250567923074613</v>
+        <v>0.53566907027150279</v>
       </c>
       <c r="H3" s="0">
-        <v>19.937494320769254</v>
+        <v>19.964330929728497</v>
       </c>
       <c r="I3" s="0">
-        <v>-1.0625056792307461</v>
+        <v>-1.0356690702715028</v>
       </c>
       <c r="J3" s="0">
-        <v>1.0625056792307461</v>
+        <v>1.0356690702715028</v>
       </c>
       <c r="K3" s="0" t="b">
         <v>0</v>
@@ -578,28 +578,28 @@
         <v>69</v>
       </c>
       <c r="C4" s="0">
-        <v>755.06500000000005</v>
+        <v>757.2885</v>
       </c>
       <c r="D4" s="0">
         <v>23.5</v>
       </c>
       <c r="E4" s="0">
-        <v>23.649640433416977</v>
+        <v>23.8973632264643</v>
       </c>
       <c r="F4" s="0">
-        <v>0.14964043341697675</v>
+        <v>0.39736322646430011</v>
       </c>
       <c r="G4" s="0">
-        <v>0.14964043341697675</v>
+        <v>0.39736322646430011</v>
       </c>
       <c r="H4" s="0">
-        <v>23.149640433416977</v>
+        <v>23.3973632264643</v>
       </c>
       <c r="I4" s="0">
-        <v>-0.35035956658302325</v>
+        <v>-0.10263677353569989</v>
       </c>
       <c r="J4" s="0">
-        <v>0.35035956658302325</v>
+        <v>0.10263677353569989</v>
       </c>
       <c r="K4" s="0" t="b">
         <v>0</v>
@@ -622,28 +622,28 @@
         <v>69</v>
       </c>
       <c r="C5" s="0">
-        <v>579.86080000000004</v>
+        <v>583.17809999999997</v>
       </c>
       <c r="D5" s="0">
         <v>21</v>
       </c>
       <c r="E5" s="0">
-        <v>19.525907231108818</v>
+        <v>19.601951630479665</v>
       </c>
       <c r="F5" s="0">
-        <v>-1.4740927688911825</v>
+        <v>-1.3980483695203354</v>
       </c>
       <c r="G5" s="0">
-        <v>1.4740927688911825</v>
+        <v>1.3980483695203354</v>
       </c>
       <c r="H5" s="0">
-        <v>19.025907231108818</v>
+        <v>19.101951630479665</v>
       </c>
       <c r="I5" s="0">
-        <v>-1.9740927688911825</v>
+        <v>-1.8980483695203354</v>
       </c>
       <c r="J5" s="0">
-        <v>1.9740927688911825</v>
+        <v>1.8980483695203354</v>
       </c>
       <c r="K5" s="0" t="b">
         <v>0</v>
@@ -666,28 +666,28 @@
         <v>69</v>
       </c>
       <c r="C6" s="0">
-        <v>634.26990000000001</v>
+        <v>633.10580000000004</v>
       </c>
       <c r="D6" s="0">
         <v>21.5</v>
       </c>
       <c r="E6" s="0">
-        <v>21.006087195620292</v>
+        <v>20.802192128563363</v>
       </c>
       <c r="F6" s="0">
-        <v>-0.49391280437970764</v>
+        <v>-0.69780787143663758</v>
       </c>
       <c r="G6" s="0">
-        <v>0.49391280437970764</v>
+        <v>0.69780787143663758</v>
       </c>
       <c r="H6" s="0">
-        <v>20.506087195620292</v>
+        <v>20.302192128563363</v>
       </c>
       <c r="I6" s="0">
-        <v>-0.99391280437970764</v>
+        <v>-1.1978078714366376</v>
       </c>
       <c r="J6" s="0">
-        <v>0.99391280437970764</v>
+        <v>1.1978078714366376</v>
       </c>
       <c r="K6" s="0" t="b">
         <v>0</v>
@@ -710,31 +710,31 @@
         <v>69</v>
       </c>
       <c r="C7" s="0">
-        <v>691.86599999999999</v>
+        <v>712.21130000000005</v>
       </c>
       <c r="D7" s="0">
         <v>22</v>
       </c>
       <c r="E7" s="0">
-        <v>21.954646683499217</v>
+        <v>22.586560035698398</v>
       </c>
       <c r="F7" s="0">
-        <v>-0.045353316500783336</v>
+        <v>0.58656003569839754</v>
       </c>
       <c r="G7" s="0">
-        <v>0.045353316500783336</v>
+        <v>0.58656003569839754</v>
       </c>
       <c r="H7" s="0">
-        <v>21.454646683499217</v>
+        <v>22.086560035698398</v>
       </c>
       <c r="I7" s="0">
-        <v>-0.54535331650078334</v>
+        <v>0.086560035698397542</v>
       </c>
       <c r="J7" s="0">
-        <v>0.54535331650078334</v>
+        <v>0.086560035698397542</v>
       </c>
       <c r="K7" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="0">
         <v>5</v>
@@ -754,28 +754,28 @@
         <v>69</v>
       </c>
       <c r="C8" s="0">
-        <v>763.82230000000004</v>
+        <v>765.37739999999997</v>
       </c>
       <c r="D8" s="0">
         <v>25</v>
       </c>
       <c r="E8" s="0">
-        <v>23.408087539604697</v>
+        <v>23.887883450789605</v>
       </c>
       <c r="F8" s="0">
-        <v>-1.591912460395303</v>
+        <v>-1.1121165492103948</v>
       </c>
       <c r="G8" s="0">
-        <v>1.591912460395303</v>
+        <v>1.1121165492103948</v>
       </c>
       <c r="H8" s="0">
-        <v>22.908087539604697</v>
+        <v>23.387883450789605</v>
       </c>
       <c r="I8" s="0">
-        <v>-2.091912460395303</v>
+        <v>-1.6121165492103948</v>
       </c>
       <c r="J8" s="0">
-        <v>2.091912460395303</v>
+        <v>1.6121165492103948</v>
       </c>
       <c r="K8" s="0" t="b">
         <v>0</v>
@@ -798,28 +798,28 @@
         <v>69</v>
       </c>
       <c r="C9" s="0">
-        <v>612.55169999999998</v>
+        <v>584.5915</v>
       </c>
       <c r="D9" s="0">
         <v>20.5</v>
       </c>
       <c r="E9" s="0">
-        <v>20.073128430802438</v>
+        <v>19.720571282242663</v>
       </c>
       <c r="F9" s="0">
-        <v>-0.4268715691975622</v>
+        <v>-0.77942871775733735</v>
       </c>
       <c r="G9" s="0">
-        <v>0.4268715691975622</v>
+        <v>0.77942871775733735</v>
       </c>
       <c r="H9" s="0">
-        <v>19.573128430802438</v>
+        <v>19.220571282242663</v>
       </c>
       <c r="I9" s="0">
-        <v>-0.9268715691975622</v>
+        <v>-1.2794287177573374</v>
       </c>
       <c r="J9" s="0">
-        <v>0.9268715691975622</v>
+        <v>1.2794287177573374</v>
       </c>
       <c r="K9" s="0" t="b">
         <v>0</v>
@@ -842,28 +842,28 @@
         <v>69</v>
       </c>
       <c r="C10" s="0">
-        <v>647.83249999999998</v>
+        <v>648.39279999999997</v>
       </c>
       <c r="D10" s="0">
         <v>21</v>
       </c>
       <c r="E10" s="0">
-        <v>20.852009792322242</v>
+        <v>20.778904825919817</v>
       </c>
       <c r="F10" s="0">
-        <v>-0.14799020767775772</v>
+        <v>-0.2210951740801832</v>
       </c>
       <c r="G10" s="0">
-        <v>0.14799020767775772</v>
+        <v>0.2210951740801832</v>
       </c>
       <c r="H10" s="0">
-        <v>20.352009792322242</v>
+        <v>20.278904825919817</v>
       </c>
       <c r="I10" s="0">
-        <v>-0.64799020767775772</v>
+        <v>-0.7210951740801832</v>
       </c>
       <c r="J10" s="0">
-        <v>0.64799020767775772</v>
+        <v>0.7210951740801832</v>
       </c>
       <c r="K10" s="0" t="b">
         <v>0</v>
@@ -886,28 +886,28 @@
         <v>69</v>
       </c>
       <c r="C11" s="0">
-        <v>468.75369999999998</v>
+        <v>466.6764</v>
       </c>
       <c r="D11" s="0">
         <v>18</v>
       </c>
       <c r="E11" s="0">
-        <v>19.081603298059882</v>
+        <v>19.288300733498179</v>
       </c>
       <c r="F11" s="0">
-        <v>1.081603298059882</v>
+        <v>1.2883007334981791</v>
       </c>
       <c r="G11" s="0">
-        <v>1.081603298059882</v>
+        <v>1.2883007334981791</v>
       </c>
       <c r="H11" s="0">
-        <v>18.581603298059882</v>
+        <v>18.788300733498179</v>
       </c>
       <c r="I11" s="0">
-        <v>0.58160329805988198</v>
+        <v>0.78830073349817908</v>
       </c>
       <c r="J11" s="0">
-        <v>0.58160329805988198</v>
+        <v>0.78830073349817908</v>
       </c>
       <c r="K11" s="0" t="b">
         <v>1</v>
@@ -930,28 +930,28 @@
         <v>69</v>
       </c>
       <c r="C12" s="0">
-        <v>745.02800000000002</v>
+        <v>747.66359999999997</v>
       </c>
       <c r="D12" s="0">
         <v>25</v>
       </c>
       <c r="E12" s="0">
-        <v>24.108970527581022</v>
+        <v>23.984337003522985</v>
       </c>
       <c r="F12" s="0">
-        <v>-0.89102947241897823</v>
+        <v>-1.0156629964770154</v>
       </c>
       <c r="G12" s="0">
-        <v>0.89102947241897823</v>
+        <v>1.0156629964770154</v>
       </c>
       <c r="H12" s="0">
-        <v>23.608970527581022</v>
+        <v>23.484337003522985</v>
       </c>
       <c r="I12" s="0">
-        <v>-1.3910294724189782</v>
+        <v>-1.5156629964770154</v>
       </c>
       <c r="J12" s="0">
-        <v>1.3910294724189782</v>
+        <v>1.5156629964770154</v>
       </c>
       <c r="K12" s="0" t="b">
         <v>0</v>
@@ -974,28 +974,28 @@
         <v>69</v>
       </c>
       <c r="C13" s="0">
-        <v>674.10310000000004</v>
+        <v>659.65279999999996</v>
       </c>
       <c r="D13" s="0">
         <v>22.5</v>
       </c>
       <c r="E13" s="0">
-        <v>21.754731044735514</v>
+        <v>21.139201363369615</v>
       </c>
       <c r="F13" s="0">
-        <v>-0.74526895526448556</v>
+        <v>-1.3607986366303848</v>
       </c>
       <c r="G13" s="0">
-        <v>0.74526895526448556</v>
+        <v>1.3607986366303848</v>
       </c>
       <c r="H13" s="0">
-        <v>21.254731044735514</v>
+        <v>20.639201363369615</v>
       </c>
       <c r="I13" s="0">
-        <v>-1.2452689552644856</v>
+        <v>-1.8607986366303848</v>
       </c>
       <c r="J13" s="0">
-        <v>1.2452689552644856</v>
+        <v>1.8607986366303848</v>
       </c>
       <c r="K13" s="0" t="b">
         <v>0</v>
@@ -1018,28 +1018,28 @@
         <v>69</v>
       </c>
       <c r="C14" s="0">
-        <v>678.64329999999995</v>
+        <v>682.95950000000005</v>
       </c>
       <c r="D14" s="0">
         <v>20.5</v>
       </c>
       <c r="E14" s="0">
-        <v>21.018563239881459</v>
+        <v>21.101957898226829</v>
       </c>
       <c r="F14" s="0">
-        <v>0.51856323988145903</v>
+        <v>0.60195789822682855</v>
       </c>
       <c r="G14" s="0">
-        <v>0.51856323988145903</v>
+        <v>0.60195789822682855</v>
       </c>
       <c r="H14" s="0">
-        <v>20.518563239881459</v>
+        <v>20.601957898226829</v>
       </c>
       <c r="I14" s="0">
-        <v>0.018563239881459026</v>
+        <v>0.10195789822682855</v>
       </c>
       <c r="J14" s="0">
-        <v>0.018563239881459026</v>
+        <v>0.10195789822682855</v>
       </c>
       <c r="K14" s="0" t="b">
         <v>1</v>
@@ -1062,28 +1062,28 @@
         <v>69</v>
       </c>
       <c r="C15" s="0">
-        <v>588.29200000000003</v>
+        <v>587.81489999999997</v>
       </c>
       <c r="D15" s="0">
         <v>19.5</v>
       </c>
       <c r="E15" s="0">
-        <v>20.434352475485877</v>
+        <v>20.349036051988367</v>
       </c>
       <c r="F15" s="0">
-        <v>0.93435247548587697</v>
+        <v>0.84903605198836729</v>
       </c>
       <c r="G15" s="0">
-        <v>0.93435247548587697</v>
+        <v>0.84903605198836729</v>
       </c>
       <c r="H15" s="0">
-        <v>19.934352475485877</v>
+        <v>19.849036051988367</v>
       </c>
       <c r="I15" s="0">
-        <v>0.43435247548587697</v>
+        <v>0.34903605198836729</v>
       </c>
       <c r="J15" s="0">
-        <v>0.43435247548587697</v>
+        <v>0.34903605198836729</v>
       </c>
       <c r="K15" s="0" t="b">
         <v>1</v>
@@ -1106,28 +1106,28 @@
         <v>69</v>
       </c>
       <c r="C16" s="0">
-        <v>618.86260000000004</v>
+        <v>624.73410000000001</v>
       </c>
       <c r="D16" s="0">
         <v>19.5</v>
       </c>
       <c r="E16" s="0">
-        <v>20.598080545242858</v>
+        <v>20.560317179877288</v>
       </c>
       <c r="F16" s="0">
-        <v>1.0980805452428584</v>
+        <v>1.0603171798772877</v>
       </c>
       <c r="G16" s="0">
-        <v>1.0980805452428584</v>
+        <v>1.0603171798772877</v>
       </c>
       <c r="H16" s="0">
-        <v>20.098080545242858</v>
+        <v>20.060317179877288</v>
       </c>
       <c r="I16" s="0">
-        <v>0.59808054524285836</v>
+        <v>0.56031717987728769</v>
       </c>
       <c r="J16" s="0">
-        <v>0.59808054524285836</v>
+        <v>0.56031717987728769</v>
       </c>
       <c r="K16" s="0" t="b">
         <v>1</v>
@@ -1150,28 +1150,28 @@
         <v>69</v>
       </c>
       <c r="C17" s="0">
-        <v>557.87480000000005</v>
+        <v>564.40920000000006</v>
       </c>
       <c r="D17" s="0">
         <v>18.5</v>
       </c>
       <c r="E17" s="0">
-        <v>19.380567479822062</v>
+        <v>19.487786264527454</v>
       </c>
       <c r="F17" s="0">
-        <v>0.88056747982206218</v>
+        <v>0.98778626452745399</v>
       </c>
       <c r="G17" s="0">
-        <v>0.88056747982206218</v>
+        <v>0.98778626452745399</v>
       </c>
       <c r="H17" s="0">
-        <v>18.880567479822062</v>
+        <v>18.987786264527454</v>
       </c>
       <c r="I17" s="0">
-        <v>0.38056747982206218</v>
+        <v>0.487786264527454</v>
       </c>
       <c r="J17" s="0">
-        <v>0.38056747982206218</v>
+        <v>0.487786264527454</v>
       </c>
       <c r="K17" s="0" t="b">
         <v>1</v>
@@ -1194,28 +1194,28 @@
         <v>69</v>
       </c>
       <c r="C18" s="0">
-        <v>734.02059999999995</v>
+        <v>736.66660000000002</v>
       </c>
       <c r="D18" s="0">
         <v>23.75</v>
       </c>
       <c r="E18" s="0">
-        <v>23.74044211134467</v>
+        <v>23.615705050608518</v>
       </c>
       <c r="F18" s="0">
-        <v>-0.0095578886553298048</v>
+        <v>-0.13429494939148157</v>
       </c>
       <c r="G18" s="0">
-        <v>0.0095578886553298048</v>
+        <v>0.13429494939148157</v>
       </c>
       <c r="H18" s="0">
-        <v>23.24044211134467</v>
+        <v>23.115705050608518</v>
       </c>
       <c r="I18" s="0">
-        <v>-0.5095578886553298</v>
+        <v>-0.63429494939148157</v>
       </c>
       <c r="J18" s="0">
-        <v>0.5095578886553298</v>
+        <v>0.63429494939148157</v>
       </c>
       <c r="K18" s="0" t="b">
         <v>0</v>
@@ -1238,28 +1238,28 @@
         <v>69</v>
       </c>
       <c r="C19" s="0">
-        <v>674.8356</v>
+        <v>676.57719999999995</v>
       </c>
       <c r="D19" s="0">
         <v>22.25</v>
       </c>
       <c r="E19" s="0">
-        <v>21.183006688972888</v>
+        <v>21.124803943722192</v>
       </c>
       <c r="F19" s="0">
-        <v>-1.0669933110271117</v>
+        <v>-1.1251960562778081</v>
       </c>
       <c r="G19" s="0">
-        <v>1.0669933110271117</v>
+        <v>1.1251960562778081</v>
       </c>
       <c r="H19" s="0">
-        <v>20.683006688972888</v>
+        <v>20.624803943722192</v>
       </c>
       <c r="I19" s="0">
-        <v>-1.5669933110271117</v>
+        <v>-1.6251960562778081</v>
       </c>
       <c r="J19" s="0">
-        <v>1.5669933110271117</v>
+        <v>1.6251960562778081</v>
       </c>
       <c r="K19" s="0" t="b">
         <v>0</v>
@@ -1282,28 +1282,28 @@
         <v>69</v>
       </c>
       <c r="C20" s="0">
-        <v>758.93589999999995</v>
+        <v>752.55830000000003</v>
       </c>
       <c r="D20" s="0">
         <v>25.5</v>
       </c>
       <c r="E20" s="0">
-        <v>23.404956077111652</v>
+        <v>23.691781206854046</v>
       </c>
       <c r="F20" s="0">
-        <v>-2.0950439228883475</v>
+        <v>-1.8082187931459544</v>
       </c>
       <c r="G20" s="0">
-        <v>2.0950439228883475</v>
+        <v>1.8082187931459544</v>
       </c>
       <c r="H20" s="0">
-        <v>22.904956077111652</v>
+        <v>23.191781206854046</v>
       </c>
       <c r="I20" s="0">
-        <v>-2.5950439228883475</v>
+        <v>-2.3082187931459544</v>
       </c>
       <c r="J20" s="0">
-        <v>2.5950439228883475</v>
+        <v>2.3082187931459544</v>
       </c>
       <c r="K20" s="0" t="b">
         <v>0</v>
@@ -1326,28 +1326,28 @@
         <v>69</v>
       </c>
       <c r="C21" s="0">
-        <v>530.03160000000003</v>
+        <v>533.39049999999998</v>
       </c>
       <c r="D21" s="0">
         <v>22.5</v>
       </c>
       <c r="E21" s="0">
-        <v>18.417233331085964</v>
+        <v>18.533588534080639</v>
       </c>
       <c r="F21" s="0">
-        <v>-4.0827666689140365</v>
+        <v>-3.9664114659193608</v>
       </c>
       <c r="G21" s="0">
-        <v>4.0827666689140365</v>
+        <v>3.9664114659193608</v>
       </c>
       <c r="H21" s="0">
-        <v>17.917233331085964</v>
+        <v>18.033588534080639</v>
       </c>
       <c r="I21" s="0">
-        <v>-4.5827666689140365</v>
+        <v>-4.4664114659193608</v>
       </c>
       <c r="J21" s="0">
-        <v>4.5827666689140365</v>
+        <v>4.4664114659193608</v>
       </c>
       <c r="K21" s="0" t="b">
         <v>0</v>
@@ -1370,28 +1370,28 @@
         <v>69</v>
       </c>
       <c r="C22" s="0">
-        <v>619.3691</v>
+        <v>617.12260000000003</v>
       </c>
       <c r="D22" s="0">
         <v>21.5</v>
       </c>
       <c r="E22" s="0">
-        <v>20.115831115231142</v>
+        <v>20.081363478276934</v>
       </c>
       <c r="F22" s="0">
-        <v>-1.384168884768858</v>
+        <v>-1.4186365217230659</v>
       </c>
       <c r="G22" s="0">
-        <v>1.384168884768858</v>
+        <v>1.4186365217230659</v>
       </c>
       <c r="H22" s="0">
-        <v>19.615831115231142</v>
+        <v>19.581363478276934</v>
       </c>
       <c r="I22" s="0">
-        <v>-1.884168884768858</v>
+        <v>-1.9186365217230659</v>
       </c>
       <c r="J22" s="0">
-        <v>1.884168884768858</v>
+        <v>1.9186365217230659</v>
       </c>
       <c r="K22" s="0" t="b">
         <v>0</v>
@@ -1414,28 +1414,28 @@
         <v>69</v>
       </c>
       <c r="C23" s="0">
-        <v>681.04340000000002</v>
+        <v>669.44370000000004</v>
       </c>
       <c r="D23" s="0">
         <v>20</v>
       </c>
       <c r="E23" s="0">
-        <v>21.914699154633759</v>
+        <v>21.631161031579019</v>
       </c>
       <c r="F23" s="0">
-        <v>1.9146991546337588</v>
+        <v>1.631161031579019</v>
       </c>
       <c r="G23" s="0">
-        <v>1.9146991546337588</v>
+        <v>1.631161031579019</v>
       </c>
       <c r="H23" s="0">
-        <v>21.414699154633759</v>
+        <v>21.131161031579019</v>
       </c>
       <c r="I23" s="0">
-        <v>1.4146991546337588</v>
+        <v>1.131161031579019</v>
       </c>
       <c r="J23" s="0">
-        <v>1.4146991546337588</v>
+        <v>1.131161031579019</v>
       </c>
       <c r="K23" s="0" t="b">
         <v>1</v>
@@ -1458,28 +1458,28 @@
         <v>69</v>
       </c>
       <c r="C24" s="0">
-        <v>585.4384</v>
+        <v>584.04089999999997</v>
       </c>
       <c r="D24" s="0">
         <v>19.5</v>
       </c>
       <c r="E24" s="0">
-        <v>19.909019532292973</v>
+        <v>19.805353319548615</v>
       </c>
       <c r="F24" s="0">
-        <v>0.40901953229297305</v>
+        <v>0.30535331954861533</v>
       </c>
       <c r="G24" s="0">
-        <v>0.40901953229297305</v>
+        <v>0.30535331954861533</v>
       </c>
       <c r="H24" s="0">
-        <v>19.409019532292973</v>
+        <v>19.305353319548615</v>
       </c>
       <c r="I24" s="0">
-        <v>-0.090980467707026946</v>
+        <v>-0.19464668045138467</v>
       </c>
       <c r="J24" s="0">
-        <v>0.090980467707026946</v>
+        <v>0.19464668045138467</v>
       </c>
       <c r="K24" s="0" t="b">
         <v>0</v>
@@ -1502,28 +1502,28 @@
         <v>69</v>
       </c>
       <c r="C25" s="0">
-        <v>581.173</v>
+        <v>583.09950000000003</v>
       </c>
       <c r="D25" s="0">
         <v>18.5</v>
       </c>
       <c r="E25" s="0">
-        <v>19.968785104804574</v>
+        <v>19.891421627213376</v>
       </c>
       <c r="F25" s="0">
-        <v>1.4687851048045744</v>
+        <v>1.3914216272133757</v>
       </c>
       <c r="G25" s="0">
-        <v>1.4687851048045744</v>
+        <v>1.3914216272133757</v>
       </c>
       <c r="H25" s="0">
-        <v>19.468785104804574</v>
+        <v>19.391421627213376</v>
       </c>
       <c r="I25" s="0">
-        <v>0.96878510480457436</v>
+        <v>0.8914216272133757</v>
       </c>
       <c r="J25" s="0">
-        <v>0.96878510480457436</v>
+        <v>0.8914216272133757</v>
       </c>
       <c r="K25" s="0" t="b">
         <v>1</v>
@@ -1546,28 +1546,28 @@
         <v>69</v>
       </c>
       <c r="C26" s="0">
-        <v>692.99239999999998</v>
+        <v>694.29290000000003</v>
       </c>
       <c r="D26" s="0">
         <v>21.25</v>
       </c>
       <c r="E26" s="0">
-        <v>22.268747188421543</v>
+        <v>22.265019204983613</v>
       </c>
       <c r="F26" s="0">
-        <v>1.0187471884215427</v>
+        <v>1.0150192049836129</v>
       </c>
       <c r="G26" s="0">
-        <v>1.0187471884215427</v>
+        <v>1.0150192049836129</v>
       </c>
       <c r="H26" s="0">
-        <v>21.768747188421543</v>
+        <v>21.765019204983613</v>
       </c>
       <c r="I26" s="0">
-        <v>0.51874718842154266</v>
+        <v>0.51501920498361287</v>
       </c>
       <c r="J26" s="0">
-        <v>0.51874718842154266</v>
+        <v>0.51501920498361287</v>
       </c>
       <c r="K26" s="0" t="b">
         <v>1</v>
@@ -1590,28 +1590,28 @@
         <v>69</v>
       </c>
       <c r="C27" s="0">
-        <v>643.06439999999998</v>
+        <v>645.69730000000004</v>
       </c>
       <c r="D27" s="0">
         <v>19.25</v>
       </c>
       <c r="E27" s="0">
-        <v>20.745212692539834</v>
+        <v>20.745992752984368</v>
       </c>
       <c r="F27" s="0">
-        <v>1.4952126925398339</v>
+        <v>1.4959927529843675</v>
       </c>
       <c r="G27" s="0">
-        <v>1.4952126925398339</v>
+        <v>1.4959927529843675</v>
       </c>
       <c r="H27" s="0">
-        <v>20.245212692539834</v>
+        <v>20.245992752984368</v>
       </c>
       <c r="I27" s="0">
-        <v>0.99521269253983391</v>
+        <v>0.99599275298436751</v>
       </c>
       <c r="J27" s="0">
-        <v>0.99521269253983391</v>
+        <v>0.99599275298436751</v>
       </c>
       <c r="K27" s="0" t="b">
         <v>1</v>
@@ -1634,28 +1634,28 @@
         <v>69</v>
       </c>
       <c r="C28" s="0">
-        <v>679.27729999999997</v>
+        <v>704.87890000000004</v>
       </c>
       <c r="D28" s="0">
         <v>21.75</v>
       </c>
       <c r="E28" s="0">
-        <v>21.353576303693472</v>
+        <v>22.00611947989659</v>
       </c>
       <c r="F28" s="0">
-        <v>-0.39642369630652752</v>
+        <v>0.25611947989659001</v>
       </c>
       <c r="G28" s="0">
-        <v>0.39642369630652752</v>
+        <v>0.25611947989659001</v>
       </c>
       <c r="H28" s="0">
-        <v>20.853576303693472</v>
+        <v>21.50611947989659</v>
       </c>
       <c r="I28" s="0">
-        <v>-0.89642369630652752</v>
+        <v>-0.24388052010340999</v>
       </c>
       <c r="J28" s="0">
-        <v>0.89642369630652752</v>
+        <v>0.24388052010340999</v>
       </c>
       <c r="K28" s="0" t="b">
         <v>0</v>
@@ -1678,28 +1678,28 @@
         <v>69</v>
       </c>
       <c r="C29" s="0">
-        <v>531.55600000000004</v>
+        <v>527.93060000000003</v>
       </c>
       <c r="D29" s="0">
         <v>20.75</v>
       </c>
       <c r="E29" s="0">
-        <v>19.082204937297267</v>
+        <v>19.1410482872183</v>
       </c>
       <c r="F29" s="0">
-        <v>-1.6677950627027336</v>
+        <v>-1.6089517127816997</v>
       </c>
       <c r="G29" s="0">
-        <v>1.6677950627027336</v>
+        <v>1.6089517127816997</v>
       </c>
       <c r="H29" s="0">
-        <v>18.582204937297267</v>
+        <v>18.6410482872183</v>
       </c>
       <c r="I29" s="0">
-        <v>-2.1677950627027336</v>
+        <v>-2.1089517127816997</v>
       </c>
       <c r="J29" s="0">
-        <v>2.1677950627027336</v>
+        <v>2.1089517127816997</v>
       </c>
       <c r="K29" s="0" t="b">
         <v>0</v>
@@ -1722,28 +1722,28 @@
         <v>69</v>
       </c>
       <c r="C30" s="0">
-        <v>685.61059999999998</v>
+        <v>688.96929999999998</v>
       </c>
       <c r="D30" s="0">
         <v>21.5</v>
       </c>
       <c r="E30" s="0">
-        <v>21.778330030685631</v>
+        <v>21.815703823855085</v>
       </c>
       <c r="F30" s="0">
-        <v>0.27833003068563045</v>
+        <v>0.31570382385508467</v>
       </c>
       <c r="G30" s="0">
-        <v>0.27833003068563045</v>
+        <v>0.31570382385508467</v>
       </c>
       <c r="H30" s="0">
-        <v>21.278330030685631</v>
+        <v>21.315703823855085</v>
       </c>
       <c r="I30" s="0">
-        <v>-0.22166996931436955</v>
+        <v>-0.18429617614491534</v>
       </c>
       <c r="J30" s="0">
-        <v>0.22166996931436955</v>
+        <v>0.18429617614491534</v>
       </c>
       <c r="K30" s="0" t="b">
         <v>0</v>
@@ -1766,28 +1766,28 @@
         <v>69</v>
       </c>
       <c r="C31" s="0">
-        <v>683.32539999999995</v>
+        <v>687.38679999999999</v>
       </c>
       <c r="D31" s="0">
         <v>19.5</v>
       </c>
       <c r="E31" s="0">
-        <v>22.014228302164447</v>
+        <v>22.044979385720652</v>
       </c>
       <c r="F31" s="0">
-        <v>2.5142283021644474</v>
+        <v>2.5449793857206515</v>
       </c>
       <c r="G31" s="0">
-        <v>2.5142283021644474</v>
+        <v>2.5449793857206515</v>
       </c>
       <c r="H31" s="0">
-        <v>21.514228302164447</v>
+        <v>21.544979385720652</v>
       </c>
       <c r="I31" s="0">
-        <v>2.0142283021644474</v>
+        <v>2.0449793857206515</v>
       </c>
       <c r="J31" s="0">
-        <v>2.0142283021644474</v>
+        <v>2.0449793857206515</v>
       </c>
       <c r="K31" s="0" t="b">
         <v>1</v>
@@ -1810,28 +1810,28 @@
         <v>69</v>
       </c>
       <c r="C32" s="0">
-        <v>669.30840000000001</v>
+        <v>664.20730000000003</v>
       </c>
       <c r="D32" s="0">
         <v>19.5</v>
       </c>
       <c r="E32" s="0">
-        <v>21.659225758580952</v>
+        <v>21.409987802133205</v>
       </c>
       <c r="F32" s="0">
-        <v>2.159225758580952</v>
+        <v>1.9099878021332053</v>
       </c>
       <c r="G32" s="0">
-        <v>2.159225758580952</v>
+        <v>1.9099878021332053</v>
       </c>
       <c r="H32" s="0">
-        <v>21.159225758580952</v>
+        <v>20.909987802133205</v>
       </c>
       <c r="I32" s="0">
-        <v>1.659225758580952</v>
+        <v>1.4099878021332053</v>
       </c>
       <c r="J32" s="0">
-        <v>1.659225758580952</v>
+        <v>1.4099878021332053</v>
       </c>
       <c r="K32" s="0" t="b">
         <v>1</v>
@@ -1854,31 +1854,31 @@
         <v>69</v>
       </c>
       <c r="C33" s="0">
-        <v>712.56219999999996</v>
+        <v>700.82140000000004</v>
       </c>
       <c r="D33" s="0">
         <v>21</v>
       </c>
       <c r="E33" s="0">
-        <v>21.758997338582411</v>
+        <v>21.493226120445865</v>
       </c>
       <c r="F33" s="0">
-        <v>0.75899733858241092</v>
+        <v>0.49322612044586478</v>
       </c>
       <c r="G33" s="0">
-        <v>0.75899733858241092</v>
+        <v>0.49322612044586478</v>
       </c>
       <c r="H33" s="0">
-        <v>21.258997338582411</v>
+        <v>20.993226120445865</v>
       </c>
       <c r="I33" s="0">
-        <v>0.25899733858241092</v>
+        <v>-0.0067738795541352204</v>
       </c>
       <c r="J33" s="0">
-        <v>0.25899733858241092</v>
+        <v>0.0067738795541352204</v>
       </c>
       <c r="K33" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" s="0">
         <v>1</v>
@@ -1898,28 +1898,28 @@
         <v>69</v>
       </c>
       <c r="C34" s="0">
-        <v>611.39670000000001</v>
+        <v>604.36569999999995</v>
       </c>
       <c r="D34" s="0">
         <v>20.25</v>
       </c>
       <c r="E34" s="0">
-        <v>20.566635624560245</v>
+        <v>20.338252438811395</v>
       </c>
       <c r="F34" s="0">
-        <v>0.31663562456024508</v>
+        <v>0.088252438811394995</v>
       </c>
       <c r="G34" s="0">
-        <v>0.31663562456024508</v>
+        <v>0.088252438811394995</v>
       </c>
       <c r="H34" s="0">
-        <v>20.066635624560245</v>
+        <v>19.838252438811395</v>
       </c>
       <c r="I34" s="0">
-        <v>-0.18336437543975492</v>
+        <v>-0.411747561188605</v>
       </c>
       <c r="J34" s="0">
-        <v>0.18336437543975492</v>
+        <v>0.411747561188605</v>
       </c>
       <c r="K34" s="0" t="b">
         <v>0</v>
@@ -1942,28 +1942,28 @@
         <v>69</v>
       </c>
       <c r="C35" s="0">
-        <v>622.68050000000005</v>
+        <v>621.61170000000004</v>
       </c>
       <c r="D35" s="0">
         <v>21.5</v>
       </c>
       <c r="E35" s="0">
-        <v>20.455945580110026</v>
+        <v>20.301393945553283</v>
       </c>
       <c r="F35" s="0">
-        <v>-1.0440544198899744</v>
+        <v>-1.1986060544467172</v>
       </c>
       <c r="G35" s="0">
-        <v>1.0440544198899744</v>
+        <v>1.1986060544467172</v>
       </c>
       <c r="H35" s="0">
-        <v>19.955945580110026</v>
+        <v>19.801393945553283</v>
       </c>
       <c r="I35" s="0">
-        <v>-1.5440544198899744</v>
+        <v>-1.6986060544467172</v>
       </c>
       <c r="J35" s="0">
-        <v>1.5440544198899744</v>
+        <v>1.6986060544467172</v>
       </c>
       <c r="K35" s="0" t="b">
         <v>0</v>
@@ -1986,28 +1986,28 @@
         <v>69</v>
       </c>
       <c r="C36" s="0">
-        <v>601.95100000000002</v>
+        <v>597.18910000000005</v>
       </c>
       <c r="D36" s="0">
         <v>19.5</v>
       </c>
       <c r="E36" s="0">
-        <v>20.166826730832764</v>
+        <v>20.001641507845868</v>
       </c>
       <c r="F36" s="0">
-        <v>0.66682673083276356</v>
+        <v>0.50164150784586781</v>
       </c>
       <c r="G36" s="0">
-        <v>0.66682673083276356</v>
+        <v>0.50164150784586781</v>
       </c>
       <c r="H36" s="0">
-        <v>19.666826730832764</v>
+        <v>19.501641507845868</v>
       </c>
       <c r="I36" s="0">
-        <v>0.16682673083276356</v>
+        <v>0.0016415078458678067</v>
       </c>
       <c r="J36" s="0">
-        <v>0.16682673083276356</v>
+        <v>0.0016415078458678067</v>
       </c>
       <c r="K36" s="0" t="b">
         <v>1</v>
@@ -2030,28 +2030,28 @@
         <v>69</v>
       </c>
       <c r="C37" s="0">
-        <v>726.80799999999999</v>
+        <v>738.8483</v>
       </c>
       <c r="D37" s="0">
         <v>25</v>
       </c>
       <c r="E37" s="0">
-        <v>22.5148311612624</v>
+        <v>22.885844580639684</v>
       </c>
       <c r="F37" s="0">
-        <v>-2.4851688387376001</v>
+        <v>-2.1141554193603156</v>
       </c>
       <c r="G37" s="0">
-        <v>2.4851688387376001</v>
+        <v>2.1141554193603156</v>
       </c>
       <c r="H37" s="0">
-        <v>22.0148311612624</v>
+        <v>22.385844580639684</v>
       </c>
       <c r="I37" s="0">
-        <v>-2.9851688387376001</v>
+        <v>-2.6141554193603156</v>
       </c>
       <c r="J37" s="0">
-        <v>2.9851688387376001</v>
+        <v>2.6141554193603156</v>
       </c>
       <c r="K37" s="0" t="b">
         <v>0</v>
@@ -2074,28 +2074,28 @@
         <v>69</v>
       </c>
       <c r="C38" s="0">
-        <v>599.73789999999997</v>
+        <v>595.78989999999999</v>
       </c>
       <c r="D38" s="0">
         <v>19</v>
       </c>
       <c r="E38" s="0">
-        <v>19.896838493016269</v>
+        <v>19.823956686981021</v>
       </c>
       <c r="F38" s="0">
-        <v>0.8968384930162685</v>
+        <v>0.82395668698102043</v>
       </c>
       <c r="G38" s="0">
-        <v>0.8968384930162685</v>
+        <v>0.82395668698102043</v>
       </c>
       <c r="H38" s="0">
-        <v>19.396838493016269</v>
+        <v>19.323956686981021</v>
       </c>
       <c r="I38" s="0">
-        <v>0.3968384930162685</v>
+        <v>0.32395668698102043</v>
       </c>
       <c r="J38" s="0">
-        <v>0.3968384930162685</v>
+        <v>0.32395668698102043</v>
       </c>
       <c r="K38" s="0" t="b">
         <v>1</v>
@@ -2118,28 +2118,28 @@
         <v>69</v>
       </c>
       <c r="C39" s="0">
-        <v>700.04589999999996</v>
+        <v>698.92719999999997</v>
       </c>
       <c r="D39" s="0">
         <v>19</v>
       </c>
       <c r="E39" s="0">
-        <v>20.109725143532462</v>
+        <v>20.398639707450201</v>
       </c>
       <c r="F39" s="0">
-        <v>1.1097251435324616</v>
+        <v>1.3986397074502008</v>
       </c>
       <c r="G39" s="0">
-        <v>1.1097251435324616</v>
+        <v>1.3986397074502008</v>
       </c>
       <c r="H39" s="0">
-        <v>19.609725143532462</v>
+        <v>19.898639707450201</v>
       </c>
       <c r="I39" s="0">
-        <v>0.60972514353246155</v>
+        <v>0.89863970745020083</v>
       </c>
       <c r="J39" s="0">
-        <v>0.60972514353246155</v>
+        <v>0.89863970745020083</v>
       </c>
       <c r="K39" s="0" t="b">
         <v>1</v>
@@ -2162,28 +2162,28 @@
         <v>69</v>
       </c>
       <c r="C40" s="0">
-        <v>776.98199999999997</v>
+        <v>762.38530000000003</v>
       </c>
       <c r="D40" s="0">
         <v>21</v>
       </c>
       <c r="E40" s="0">
-        <v>23.748642067456501</v>
+        <v>23.601386109442707</v>
       </c>
       <c r="F40" s="0">
-        <v>2.7486420674565011</v>
+        <v>2.6013861094427071</v>
       </c>
       <c r="G40" s="0">
-        <v>2.7486420674565011</v>
+        <v>2.6013861094427071</v>
       </c>
       <c r="H40" s="0">
-        <v>23.248642067456501</v>
+        <v>23.101386109442707</v>
       </c>
       <c r="I40" s="0">
-        <v>2.2486420674565011</v>
+        <v>2.1013861094427071</v>
       </c>
       <c r="J40" s="0">
-        <v>2.2486420674565011</v>
+        <v>2.1013861094427071</v>
       </c>
       <c r="K40" s="0" t="b">
         <v>1</v>
@@ -2206,28 +2206,28 @@
         <v>69</v>
       </c>
       <c r="C41" s="0">
-        <v>673.32410000000004</v>
+        <v>672.51900000000001</v>
       </c>
       <c r="D41" s="0">
         <v>20.5</v>
       </c>
       <c r="E41" s="0">
-        <v>21.351311293723949</v>
+        <v>21.273364363283349</v>
       </c>
       <c r="F41" s="0">
-        <v>0.85131129372394909</v>
+        <v>0.77336436328334912</v>
       </c>
       <c r="G41" s="0">
-        <v>0.85131129372394909</v>
+        <v>0.77336436328334912</v>
       </c>
       <c r="H41" s="0">
-        <v>20.851311293723949</v>
+        <v>20.773364363283349</v>
       </c>
       <c r="I41" s="0">
-        <v>0.35131129372394909</v>
+        <v>0.27336436328334912</v>
       </c>
       <c r="J41" s="0">
-        <v>0.35131129372394909</v>
+        <v>0.27336436328334912</v>
       </c>
       <c r="K41" s="0" t="b">
         <v>1</v>
@@ -2250,28 +2250,28 @@
         <v>69</v>
       </c>
       <c r="C42" s="0">
-        <v>526.36469999999997</v>
+        <v>523.23350000000005</v>
       </c>
       <c r="D42" s="0">
         <v>19.25</v>
       </c>
       <c r="E42" s="0">
-        <v>19.12980026837257</v>
+        <v>19.090539729661465</v>
       </c>
       <c r="F42" s="0">
-        <v>-0.12019973162743014</v>
+        <v>-0.15946027033853483</v>
       </c>
       <c r="G42" s="0">
-        <v>0.12019973162743014</v>
+        <v>0.15946027033853483</v>
       </c>
       <c r="H42" s="0">
-        <v>18.62980026837257</v>
+        <v>18.590539729661465</v>
       </c>
       <c r="I42" s="0">
-        <v>-0.62019973162743014</v>
+        <v>-0.65946027033853483</v>
       </c>
       <c r="J42" s="0">
-        <v>0.62019973162743014</v>
+        <v>0.65946027033853483</v>
       </c>
       <c r="K42" s="0" t="b">
         <v>0</v>
@@ -2294,28 +2294,28 @@
         <v>69</v>
       </c>
       <c r="C43" s="0">
-        <v>586.85530000000006</v>
+        <v>585.99260000000004</v>
       </c>
       <c r="D43" s="0">
         <v>20</v>
       </c>
       <c r="E43" s="0">
-        <v>19.600739334387431</v>
+        <v>19.629735863092161</v>
       </c>
       <c r="F43" s="0">
-        <v>-0.39926066561256946</v>
+        <v>-0.37026413690783855</v>
       </c>
       <c r="G43" s="0">
-        <v>0.39926066561256946</v>
+        <v>0.37026413690783855</v>
       </c>
       <c r="H43" s="0">
-        <v>19.100739334387431</v>
+        <v>19.129735863092161</v>
       </c>
       <c r="I43" s="0">
-        <v>-0.89926066561256946</v>
+        <v>-0.87026413690783855</v>
       </c>
       <c r="J43" s="0">
-        <v>0.89926066561256946</v>
+        <v>0.87026413690783855</v>
       </c>
       <c r="K43" s="0" t="b">
         <v>0</v>
@@ -2338,28 +2338,28 @@
         <v>69</v>
       </c>
       <c r="C44" s="0">
-        <v>663.21749999999997</v>
+        <v>661.50829999999996</v>
       </c>
       <c r="D44" s="0">
         <v>20</v>
       </c>
       <c r="E44" s="0">
-        <v>21.130369959153626</v>
+        <v>20.962302862798499</v>
       </c>
       <c r="F44" s="0">
-        <v>1.1303699591536258</v>
+        <v>0.96230286279849864</v>
       </c>
       <c r="G44" s="0">
-        <v>1.1303699591536258</v>
+        <v>0.96230286279849864</v>
       </c>
       <c r="H44" s="0">
-        <v>20.630369959153626</v>
+        <v>20.462302862798499</v>
       </c>
       <c r="I44" s="0">
-        <v>0.63036995915362581</v>
+        <v>0.46230286279849864</v>
       </c>
       <c r="J44" s="0">
-        <v>0.63036995915362581</v>
+        <v>0.46230286279849864</v>
       </c>
       <c r="K44" s="0" t="b">
         <v>1</v>
@@ -2382,28 +2382,28 @@
         <v>69</v>
       </c>
       <c r="C45" s="0">
-        <v>582.90459999999996</v>
+        <v>579.78219999999999</v>
       </c>
       <c r="D45" s="0">
         <v>20</v>
       </c>
       <c r="E45" s="0">
-        <v>19.963563699796481</v>
+        <v>19.847229478702079</v>
       </c>
       <c r="F45" s="0">
-        <v>-0.036436300203519068</v>
+        <v>-0.15277052129792068</v>
       </c>
       <c r="G45" s="0">
-        <v>0.036436300203519068</v>
+        <v>0.15277052129792068</v>
       </c>
       <c r="H45" s="0">
-        <v>19.463563699796481</v>
+        <v>19.347229478702079</v>
       </c>
       <c r="I45" s="0">
-        <v>-0.53643630020351907</v>
+        <v>-0.65277052129792068</v>
       </c>
       <c r="J45" s="0">
-        <v>0.53643630020351907</v>
+        <v>0.65277052129792068</v>
       </c>
       <c r="K45" s="0" t="b">
         <v>0</v>
@@ -2426,28 +2426,28 @@
         <v>69</v>
       </c>
       <c r="C46" s="0">
-        <v>732.64890000000003</v>
+        <v>725.4751</v>
       </c>
       <c r="D46" s="0">
         <v>22</v>
       </c>
       <c r="E46" s="0">
-        <v>24.299107014904109</v>
+        <v>23.714954897495979</v>
       </c>
       <c r="F46" s="0">
-        <v>2.2991070149041093</v>
+        <v>1.7149548974959785</v>
       </c>
       <c r="G46" s="0">
-        <v>2.2991070149041093</v>
+        <v>1.7149548974959785</v>
       </c>
       <c r="H46" s="0">
-        <v>23.799107014904109</v>
+        <v>23.214954897495979</v>
       </c>
       <c r="I46" s="0">
-        <v>1.7991070149041093</v>
+        <v>1.2149548974959785</v>
       </c>
       <c r="J46" s="0">
-        <v>1.7991070149041093</v>
+        <v>1.2149548974959785</v>
       </c>
       <c r="K46" s="0" t="b">
         <v>1</v>
@@ -2470,31 +2470,31 @@
         <v>69</v>
       </c>
       <c r="C47" s="0">
-        <v>704.21619999999996</v>
+        <v>700.72990000000004</v>
       </c>
       <c r="D47" s="0">
         <v>22</v>
       </c>
       <c r="E47" s="0">
-        <v>22.735432536726279</v>
+        <v>22.493454106758119</v>
       </c>
       <c r="F47" s="0">
-        <v>0.73543253672627884</v>
+        <v>0.49345410675811863</v>
       </c>
       <c r="G47" s="0">
-        <v>0.73543253672627884</v>
+        <v>0.49345410675811863</v>
       </c>
       <c r="H47" s="0">
-        <v>22.235432536726279</v>
+        <v>21.993454106758119</v>
       </c>
       <c r="I47" s="0">
-        <v>0.23543253672627884</v>
+        <v>-0.0065458932418813731</v>
       </c>
       <c r="J47" s="0">
-        <v>0.23543253672627884</v>
+        <v>0.0065458932418813731</v>
       </c>
       <c r="K47" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="0">
         <v>3</v>
@@ -2514,28 +2514,28 @@
         <v>69</v>
       </c>
       <c r="C48" s="0">
-        <v>707.67989999999998</v>
+        <v>697.40779999999995</v>
       </c>
       <c r="D48" s="0">
         <v>23</v>
       </c>
       <c r="E48" s="0">
-        <v>22.070499914635604</v>
+        <v>21.840840602271516</v>
       </c>
       <c r="F48" s="0">
-        <v>-0.92950008536439555</v>
+        <v>-1.1591593977284838</v>
       </c>
       <c r="G48" s="0">
-        <v>0.92950008536439555</v>
+        <v>1.1591593977284838</v>
       </c>
       <c r="H48" s="0">
-        <v>21.570499914635604</v>
+        <v>21.340840602271516</v>
       </c>
       <c r="I48" s="0">
-        <v>-1.4295000853643955</v>
+        <v>-1.6591593977284838</v>
       </c>
       <c r="J48" s="0">
-        <v>1.4295000853643955</v>
+        <v>1.6591593977284838</v>
       </c>
       <c r="K48" s="0" t="b">
         <v>0</v>
@@ -2558,28 +2558,28 @@
         <v>69</v>
       </c>
       <c r="C49" s="0">
-        <v>666.81700000000001</v>
+        <v>664.56500000000005</v>
       </c>
       <c r="D49" s="0">
         <v>21.75</v>
       </c>
       <c r="E49" s="0">
-        <v>21.101204944293261</v>
+        <v>20.943701362253084</v>
       </c>
       <c r="F49" s="0">
-        <v>-0.64879505570673857</v>
+        <v>-0.80629863774691657</v>
       </c>
       <c r="G49" s="0">
-        <v>0.64879505570673857</v>
+        <v>0.80629863774691657</v>
       </c>
       <c r="H49" s="0">
-        <v>20.601204944293261</v>
+        <v>20.443701362253084</v>
       </c>
       <c r="I49" s="0">
-        <v>-1.1487950557067386</v>
+        <v>-1.3062986377469166</v>
       </c>
       <c r="J49" s="0">
-        <v>1.1487950557067386</v>
+        <v>1.3062986377469166</v>
       </c>
       <c r="K49" s="0" t="b">
         <v>0</v>
@@ -2602,28 +2602,28 @@
         <v>69</v>
       </c>
       <c r="C50" s="0">
-        <v>688.77390000000003</v>
+        <v>689.15930000000003</v>
       </c>
       <c r="D50" s="0">
         <v>21.5</v>
       </c>
       <c r="E50" s="0">
-        <v>21.564966619938438</v>
+        <v>21.548713042527616</v>
       </c>
       <c r="F50" s="0">
-        <v>0.064966619938438441</v>
+        <v>0.048713042527616324</v>
       </c>
       <c r="G50" s="0">
-        <v>0.064966619938438441</v>
+        <v>0.048713042527616324</v>
       </c>
       <c r="H50" s="0">
-        <v>21.064966619938438</v>
+        <v>21.048713042527616</v>
       </c>
       <c r="I50" s="0">
-        <v>-0.43503338006156156</v>
+        <v>-0.45128695747238368</v>
       </c>
       <c r="J50" s="0">
-        <v>0.43503338006156156</v>
+        <v>0.45128695747238368</v>
       </c>
       <c r="K50" s="0" t="b">
         <v>0</v>
@@ -2646,28 +2646,28 @@
         <v>69</v>
       </c>
       <c r="C51" s="0">
-        <v>615.82560000000001</v>
+        <v>610.64480000000003</v>
       </c>
       <c r="D51" s="0">
         <v>19.199999999999999</v>
       </c>
       <c r="E51" s="0">
-        <v>20.297450716701004</v>
+        <v>20.129063444935426</v>
       </c>
       <c r="F51" s="0">
-        <v>1.0974507167010046</v>
+        <v>0.92906344493542647</v>
       </c>
       <c r="G51" s="0">
-        <v>1.0974507167010046</v>
+        <v>0.92906344493542647</v>
       </c>
       <c r="H51" s="0">
-        <v>19.797450716701004</v>
+        <v>19.629063444935426</v>
       </c>
       <c r="I51" s="0">
-        <v>0.59745071670100458</v>
+        <v>0.42906344493542648</v>
       </c>
       <c r="J51" s="0">
-        <v>0.59745071670100458</v>
+        <v>0.42906344493542648</v>
       </c>
       <c r="K51" s="0" t="b">
         <v>1</v>
@@ -2690,28 +2690,28 @@
         <v>69</v>
       </c>
       <c r="C52" s="0">
-        <v>568.91740000000004</v>
+        <v>576.71630000000005</v>
       </c>
       <c r="D52" s="0">
         <v>17.5</v>
       </c>
       <c r="E52" s="0">
-        <v>19.738454519574312</v>
+        <v>19.77873962081226</v>
       </c>
       <c r="F52" s="0">
-        <v>2.2384545195743115</v>
+        <v>2.2787396208122601</v>
       </c>
       <c r="G52" s="0">
-        <v>2.2384545195743115</v>
+        <v>2.2787396208122601</v>
       </c>
       <c r="H52" s="0">
-        <v>19.238454519574312</v>
+        <v>19.27873962081226</v>
       </c>
       <c r="I52" s="0">
-        <v>1.7384545195743115</v>
+        <v>1.7787396208122601</v>
       </c>
       <c r="J52" s="0">
-        <v>1.7384545195743115</v>
+        <v>1.7787396208122601</v>
       </c>
       <c r="K52" s="0" t="b">
         <v>1</v>
@@ -2734,28 +2734,28 @@
         <v>69</v>
       </c>
       <c r="C53" s="0">
-        <v>594.03499999999997</v>
+        <v>598.05470000000003</v>
       </c>
       <c r="D53" s="0">
         <v>18.399999999999999</v>
       </c>
       <c r="E53" s="0">
-        <v>19.920713124577375</v>
+        <v>19.947002364420335</v>
       </c>
       <c r="F53" s="0">
-        <v>1.5207131245773766</v>
+        <v>1.5470023644203366</v>
       </c>
       <c r="G53" s="0">
-        <v>1.5207131245773766</v>
+        <v>1.5470023644203366</v>
       </c>
       <c r="H53" s="0">
-        <v>19.420713124577375</v>
+        <v>19.447002364420335</v>
       </c>
       <c r="I53" s="0">
-        <v>1.0207131245773766</v>
+        <v>1.0470023644203366</v>
       </c>
       <c r="J53" s="0">
-        <v>1.0207131245773766</v>
+        <v>1.0470023644203366</v>
       </c>
       <c r="K53" s="0" t="b">
         <v>1</v>
@@ -2778,28 +2778,28 @@
         <v>69</v>
       </c>
       <c r="C54" s="0">
-        <v>566.51940000000002</v>
+        <v>573.06939999999997</v>
       </c>
       <c r="D54" s="0">
         <v>19</v>
       </c>
       <c r="E54" s="0">
-        <v>19.532823848349199</v>
+        <v>19.625533753311757</v>
       </c>
       <c r="F54" s="0">
-        <v>0.53282384834919938</v>
+        <v>0.62553375331175687</v>
       </c>
       <c r="G54" s="0">
-        <v>0.53282384834919938</v>
+        <v>0.62553375331175687</v>
       </c>
       <c r="H54" s="0">
-        <v>19.032823848349199</v>
+        <v>19.125533753311757</v>
       </c>
       <c r="I54" s="0">
-        <v>0.03282384834919938</v>
+        <v>0.12553375331175687</v>
       </c>
       <c r="J54" s="0">
-        <v>0.03282384834919938</v>
+        <v>0.12553375331175687</v>
       </c>
       <c r="K54" s="0" t="b">
         <v>1</v>
@@ -2822,28 +2822,28 @@
         <v>69</v>
       </c>
       <c r="C55" s="0">
-        <v>614.26739999999995</v>
+        <v>610.65390000000002</v>
       </c>
       <c r="D55" s="0">
         <v>19.5</v>
       </c>
       <c r="E55" s="0">
-        <v>20.252026655178678</v>
+        <v>20.114772213833486</v>
       </c>
       <c r="F55" s="0">
-        <v>0.75202665517867828</v>
+        <v>0.61477221383348635</v>
       </c>
       <c r="G55" s="0">
-        <v>0.75202665517867828</v>
+        <v>0.61477221383348635</v>
       </c>
       <c r="H55" s="0">
-        <v>19.752026655178678</v>
+        <v>19.614772213833486</v>
       </c>
       <c r="I55" s="0">
-        <v>0.25202665517867828</v>
+        <v>0.11477221383348635</v>
       </c>
       <c r="J55" s="0">
-        <v>0.25202665517867828</v>
+        <v>0.11477221383348635</v>
       </c>
       <c r="K55" s="0" t="b">
         <v>1</v>
@@ -2866,28 +2866,28 @@
         <v>69</v>
       </c>
       <c r="C56" s="0">
-        <v>717.47789999999998</v>
+        <v>701.03470000000004</v>
       </c>
       <c r="D56" s="0">
         <v>20.5</v>
       </c>
       <c r="E56" s="0">
-        <v>22.501810412115908</v>
+        <v>21.956468192337773</v>
       </c>
       <c r="F56" s="0">
-        <v>2.0018104121159084</v>
+        <v>1.4564681923377734</v>
       </c>
       <c r="G56" s="0">
-        <v>2.0018104121159084</v>
+        <v>1.4564681923377734</v>
       </c>
       <c r="H56" s="0">
-        <v>22.001810412115908</v>
+        <v>21.456468192337773</v>
       </c>
       <c r="I56" s="0">
-        <v>1.5018104121159084</v>
+        <v>0.95646819233777336</v>
       </c>
       <c r="J56" s="0">
-        <v>1.5018104121159084</v>
+        <v>0.95646819233777336</v>
       </c>
       <c r="K56" s="0" t="b">
         <v>1</v>
@@ -2910,28 +2910,28 @@
         <v>69</v>
       </c>
       <c r="C57" s="0">
-        <v>656.12369999999999</v>
+        <v>647.98350000000005</v>
       </c>
       <c r="D57" s="0">
         <v>21</v>
       </c>
       <c r="E57" s="0">
-        <v>20.830567540357542</v>
+        <v>20.575523939993058</v>
       </c>
       <c r="F57" s="0">
-        <v>-0.1694324596424579</v>
+        <v>-0.42447606000694194</v>
       </c>
       <c r="G57" s="0">
-        <v>0.1694324596424579</v>
+        <v>0.42447606000694194</v>
       </c>
       <c r="H57" s="0">
-        <v>20.330567540357542</v>
+        <v>20.075523939993058</v>
       </c>
       <c r="I57" s="0">
-        <v>-0.6694324596424579</v>
+        <v>-0.92447606000694194</v>
       </c>
       <c r="J57" s="0">
-        <v>0.6694324596424579</v>
+        <v>0.92447606000694194</v>
       </c>
       <c r="K57" s="0" t="b">
         <v>0</v>
@@ -2954,28 +2954,28 @@
         <v>69</v>
       </c>
       <c r="C58" s="0">
-        <v>713.17060000000004</v>
+        <v>713.38980000000004</v>
       </c>
       <c r="D58" s="0">
         <v>23.5</v>
       </c>
       <c r="E58" s="0">
-        <v>21.93208406768094</v>
+        <v>21.989360814281056</v>
       </c>
       <c r="F58" s="0">
-        <v>-1.5679159323190604</v>
+        <v>-1.5106391857189436</v>
       </c>
       <c r="G58" s="0">
-        <v>1.5679159323190604</v>
+        <v>1.5106391857189436</v>
       </c>
       <c r="H58" s="0">
-        <v>21.43208406768094</v>
+        <v>21.489360814281056</v>
       </c>
       <c r="I58" s="0">
-        <v>-2.0679159323190604</v>
+        <v>-2.0106391857189436</v>
       </c>
       <c r="J58" s="0">
-        <v>2.0679159323190604</v>
+        <v>2.0106391857189436</v>
       </c>
       <c r="K58" s="0" t="b">
         <v>0</v>
@@ -2998,28 +2998,28 @@
         <v>69</v>
       </c>
       <c r="C59" s="0">
-        <v>675.12120000000004</v>
+        <v>672.01580000000001</v>
       </c>
       <c r="D59" s="0">
         <v>20.5</v>
       </c>
       <c r="E59" s="0">
-        <v>21.296960252043835</v>
+        <v>21.180567765541262</v>
       </c>
       <c r="F59" s="0">
-        <v>0.79696025204383503</v>
+        <v>0.6805677655412623</v>
       </c>
       <c r="G59" s="0">
-        <v>0.79696025204383503</v>
+        <v>0.6805677655412623</v>
       </c>
       <c r="H59" s="0">
-        <v>20.796960252043835</v>
+        <v>20.680567765541262</v>
       </c>
       <c r="I59" s="0">
-        <v>0.29696025204383503</v>
+        <v>0.1805677655412623</v>
       </c>
       <c r="J59" s="0">
-        <v>0.29696025204383503</v>
+        <v>0.1805677655412623</v>
       </c>
       <c r="K59" s="0" t="b">
         <v>1</v>
@@ -3042,28 +3042,28 @@
         <v>69</v>
       </c>
       <c r="C60" s="0">
-        <v>689.68129999999997</v>
+        <v>697.428</v>
       </c>
       <c r="D60" s="0">
         <v>21.5</v>
       </c>
       <c r="E60" s="0">
-        <v>21.400137657767285</v>
+        <v>21.565728463627369</v>
       </c>
       <c r="F60" s="0">
-        <v>-0.099862342232714951</v>
+        <v>0.065728463627369394</v>
       </c>
       <c r="G60" s="0">
-        <v>0.099862342232714951</v>
+        <v>0.065728463627369394</v>
       </c>
       <c r="H60" s="0">
-        <v>20.900137657767285</v>
+        <v>21.065728463627369</v>
       </c>
       <c r="I60" s="0">
-        <v>-0.59986234223271495</v>
+        <v>-0.43427153637263061</v>
       </c>
       <c r="J60" s="0">
-        <v>0.59986234223271495</v>
+        <v>0.43427153637263061</v>
       </c>
       <c r="K60" s="0" t="b">
         <v>0</v>
@@ -3086,28 +3086,28 @@
         <v>69</v>
       </c>
       <c r="C61" s="0">
-        <v>646.9873</v>
+        <v>648.5258</v>
       </c>
       <c r="D61" s="0">
         <v>20</v>
       </c>
       <c r="E61" s="0">
-        <v>20.500889305829464</v>
+        <v>20.515607960658762</v>
       </c>
       <c r="F61" s="0">
-        <v>0.50088930582946389</v>
+        <v>0.51560796065876247</v>
       </c>
       <c r="G61" s="0">
-        <v>0.50088930582946389</v>
+        <v>0.51560796065876247</v>
       </c>
       <c r="H61" s="0">
-        <v>20.000889305829464</v>
+        <v>20.015607960658762</v>
       </c>
       <c r="I61" s="0">
-        <v>0.00088930582946389336</v>
+        <v>0.015607960658762465</v>
       </c>
       <c r="J61" s="0">
-        <v>0.00088930582946389336</v>
+        <v>0.015607960658762465</v>
       </c>
       <c r="K61" s="0" t="b">
         <v>1</v>
@@ -3130,28 +3130,28 @@
         <v>69</v>
       </c>
       <c r="C62" s="0">
-        <v>680.14350000000002</v>
+        <v>690.99220000000003</v>
       </c>
       <c r="D62" s="0">
         <v>23</v>
       </c>
       <c r="E62" s="0">
-        <v>21.123036057278341</v>
+        <v>21.33432619022226</v>
       </c>
       <c r="F62" s="0">
-        <v>-1.8769639427216589</v>
+        <v>-1.6656738097777399</v>
       </c>
       <c r="G62" s="0">
-        <v>1.8769639427216589</v>
+        <v>1.6656738097777399</v>
       </c>
       <c r="H62" s="0">
-        <v>20.623036057278341</v>
+        <v>20.83432619022226</v>
       </c>
       <c r="I62" s="0">
-        <v>-2.3769639427216589</v>
+        <v>-2.1656738097777399</v>
       </c>
       <c r="J62" s="0">
-        <v>2.3769639427216589</v>
+        <v>2.1656738097777399</v>
       </c>
       <c r="K62" s="0" t="b">
         <v>0</v>
@@ -3174,28 +3174,28 @@
         <v>69</v>
       </c>
       <c r="C63" s="0">
-        <v>675.0444</v>
+        <v>674.3954</v>
       </c>
       <c r="D63" s="0">
         <v>21.5</v>
       </c>
       <c r="E63" s="0">
-        <v>21.235582286319343</v>
+        <v>21.12822064790215</v>
       </c>
       <c r="F63" s="0">
-        <v>-0.26441771368065759</v>
+        <v>-0.37177935209784962</v>
       </c>
       <c r="G63" s="0">
-        <v>0.26441771368065759</v>
+        <v>0.37177935209784962</v>
       </c>
       <c r="H63" s="0">
-        <v>20.735582286319343</v>
+        <v>20.62822064790215</v>
       </c>
       <c r="I63" s="0">
-        <v>-0.76441771368065758</v>
+        <v>-0.87177935209784962</v>
       </c>
       <c r="J63" s="0">
-        <v>0.76441771368065758</v>
+        <v>0.87177935209784962</v>
       </c>
       <c r="K63" s="0" t="b">
         <v>0</v>
@@ -3218,28 +3218,28 @@
         <v>69</v>
       </c>
       <c r="C64" s="0">
-        <v>638.85119999999995</v>
+        <v>643.54809999999998</v>
       </c>
       <c r="D64" s="0">
         <v>22.5</v>
       </c>
       <c r="E64" s="0">
-        <v>20.60403726506501</v>
+        <v>20.593001913874225</v>
       </c>
       <c r="F64" s="0">
-        <v>-1.8959627349349901</v>
+        <v>-1.9069980861257747</v>
       </c>
       <c r="G64" s="0">
-        <v>1.8959627349349901</v>
+        <v>1.9069980861257747</v>
       </c>
       <c r="H64" s="0">
-        <v>20.10403726506501</v>
+        <v>20.093001913874225</v>
       </c>
       <c r="I64" s="0">
-        <v>-2.3959627349349901</v>
+        <v>-2.4069980861257747</v>
       </c>
       <c r="J64" s="0">
-        <v>2.3959627349349901</v>
+        <v>2.4069980861257747</v>
       </c>
       <c r="K64" s="0" t="b">
         <v>0</v>
@@ -3262,28 +3262,28 @@
         <v>69</v>
       </c>
       <c r="C65" s="0">
-        <v>595.31380000000001</v>
+        <v>597.84789999999998</v>
       </c>
       <c r="D65" s="0">
         <v>19.25</v>
       </c>
       <c r="E65" s="0">
-        <v>19.771902609257364</v>
+        <v>19.833197448405919</v>
       </c>
       <c r="F65" s="0">
-        <v>0.52190260925736354</v>
+        <v>0.58319744840591881</v>
       </c>
       <c r="G65" s="0">
-        <v>0.52190260925736354</v>
+        <v>0.58319744840591881</v>
       </c>
       <c r="H65" s="0">
-        <v>19.271902609257364</v>
+        <v>19.333197448405919</v>
       </c>
       <c r="I65" s="0">
-        <v>0.021902609257363537</v>
+        <v>0.083197448405918806</v>
       </c>
       <c r="J65" s="0">
-        <v>0.021902609257363537</v>
+        <v>0.083197448405918806</v>
       </c>
       <c r="K65" s="0" t="b">
         <v>1</v>
@@ -3306,28 +3306,28 @@
         <v>69</v>
       </c>
       <c r="C66" s="0">
-        <v>698.0498</v>
+        <v>710.17049999999995</v>
       </c>
       <c r="D66" s="0">
         <v>23.5</v>
       </c>
       <c r="E66" s="0">
-        <v>21.731312678014401</v>
+        <v>22.01787509888468</v>
       </c>
       <c r="F66" s="0">
-        <v>-1.768687321985599</v>
+        <v>-1.4821249011153199</v>
       </c>
       <c r="G66" s="0">
-        <v>1.768687321985599</v>
+        <v>1.4821249011153199</v>
       </c>
       <c r="H66" s="0">
-        <v>21.231312678014401</v>
+        <v>21.51787509888468</v>
       </c>
       <c r="I66" s="0">
-        <v>-2.268687321985599</v>
+        <v>-1.9821249011153199</v>
       </c>
       <c r="J66" s="0">
-        <v>2.268687321985599</v>
+        <v>1.9821249011153199</v>
       </c>
       <c r="K66" s="0" t="b">
         <v>0</v>
@@ -3350,28 +3350,28 @@
         <v>69</v>
       </c>
       <c r="C67" s="0">
-        <v>634.08339999999998</v>
+        <v>639.05380000000002</v>
       </c>
       <c r="D67" s="0">
         <v>21.5</v>
       </c>
       <c r="E67" s="0">
-        <v>20.552128595616768</v>
+        <v>20.499677366091266</v>
       </c>
       <c r="F67" s="0">
-        <v>-0.94787140438323192</v>
+        <v>-1.0003226339087341</v>
       </c>
       <c r="G67" s="0">
-        <v>0.94787140438323192</v>
+        <v>1.0003226339087341</v>
       </c>
       <c r="H67" s="0">
-        <v>20.052128595616768</v>
+        <v>19.999677366091266</v>
       </c>
       <c r="I67" s="0">
-        <v>-1.4478714043832319</v>
+        <v>-1.5003226339087341</v>
       </c>
       <c r="J67" s="0">
-        <v>1.4478714043832319</v>
+        <v>1.5003226339087341</v>
       </c>
       <c r="K67" s="0" t="b">
         <v>0</v>
@@ -3394,28 +3394,28 @@
         <v>69</v>
       </c>
       <c r="C68" s="0">
-        <v>578.7296</v>
+        <v>581.15859999999998</v>
       </c>
       <c r="D68" s="0">
         <v>19</v>
       </c>
       <c r="E68" s="0">
-        <v>19.833218955635616</v>
+        <v>19.813930729287005</v>
       </c>
       <c r="F68" s="0">
-        <v>0.83321895563561554</v>
+        <v>0.81393072928700505</v>
       </c>
       <c r="G68" s="0">
-        <v>0.83321895563561554</v>
+        <v>0.81393072928700505</v>
       </c>
       <c r="H68" s="0">
-        <v>19.333218955635616</v>
+        <v>19.313930729287005</v>
       </c>
       <c r="I68" s="0">
-        <v>0.33321895563561554</v>
+        <v>0.31393072928700505</v>
       </c>
       <c r="J68" s="0">
-        <v>0.33321895563561554</v>
+        <v>0.31393072928700505</v>
       </c>
       <c r="K68" s="0" t="b">
         <v>1</v>
@@ -3476,16 +3476,16 @@
         <v>85</v>
       </c>
       <c r="B2" s="0">
-        <v>1.0820000000000001</v>
+        <v>1.0600000000000001</v>
       </c>
       <c r="C2" s="0">
-        <v>1.355</v>
+        <v>1.2949999999999999</v>
       </c>
       <c r="D2" s="0">
-        <v>0.42899999999999999</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="E2" s="0">
-        <v>0.060999999999999999</v>
+        <v>0.034000000000000002</v>
       </c>
       <c r="F2" s="0"/>
       <c r="G2" s="0"/>
@@ -3529,18 +3529,18 @@
         <v>88</v>
       </c>
       <c r="B5" s="0">
-        <v>1.0980000000000001</v>
+        <v>1.054</v>
       </c>
       <c r="C5" s="0"/>
       <c r="D5" s="0"/>
       <c r="E5" s="0">
-        <v>-0.439</v>
+        <v>-0.46600000000000003</v>
       </c>
       <c r="F5" s="0">
-        <v>58.200000000000003</v>
+        <v>56.700000000000003</v>
       </c>
       <c r="G5" s="0">
-        <v>44.799999999999997</v>
+        <v>43.299999999999997</v>
       </c>
     </row>
     <row r="6">
@@ -3548,16 +3548,16 @@
         <v>89</v>
       </c>
       <c r="B6" s="0">
-        <v>1.0940000000000001</v>
+        <v>1.087</v>
       </c>
       <c r="C6" s="0">
-        <v>1.3859999999999999</v>
+        <v>1.359</v>
       </c>
       <c r="D6" s="0">
-        <v>0.39700000000000002</v>
+        <v>0.41999999999999999</v>
       </c>
       <c r="E6" s="0">
-        <v>0.014999999999999999</v>
+        <v>0.010999999999999999</v>
       </c>
       <c r="F6" s="0"/>
       <c r="G6" s="0"/>
@@ -3567,15 +3567,15 @@
         <v>90</v>
       </c>
       <c r="B7" s="0">
-        <v>1.157</v>
+        <v>1.127</v>
       </c>
       <c r="C7" s="0"/>
       <c r="D7" s="0"/>
       <c r="E7" s="0">
-        <v>-0.48499999999999999</v>
+        <v>-0.48899999999999999</v>
       </c>
       <c r="F7" s="0">
-        <v>55.200000000000003</v>
+        <v>50.700000000000003</v>
       </c>
       <c r="G7" s="0">
         <v>38.799999999999997</v>
@@ -3688,13 +3688,13 @@
         <v>112</v>
       </c>
       <c r="B2" s="0">
-        <v>9.7510999999999992</v>
+        <v>9.4699000000000009</v>
       </c>
       <c r="C2" s="0">
-        <v>1.7554000000000001</v>
+        <v>1.7356</v>
       </c>
       <c r="D2" s="0">
-        <v>5.5549999999999997</v>
+        <v>5.4560000000000004</v>
       </c>
       <c r="E2" s="0">
         <v>0</v>
@@ -3705,13 +3705,13 @@
         <v>113</v>
       </c>
       <c r="B3" s="0">
-        <v>0.018200000000000001</v>
+        <v>0.018599999999999999</v>
       </c>
       <c r="C3" s="0">
-        <v>0.0025999999999999999</v>
+        <v>0.0025000000000000001</v>
       </c>
       <c r="D3" s="0">
-        <v>7.077</v>
+        <v>7.3230000000000004</v>
       </c>
       <c r="E3" s="0">
         <v>0</v>
@@ -3722,16 +3722,16 @@
         <v>114</v>
       </c>
       <c r="B4" s="0">
-        <v>-0.013899999999999999</v>
+        <v>-0.012699999999999999</v>
       </c>
       <c r="C4" s="0">
-        <v>0.0099000000000000008</v>
+        <v>0.0097999999999999997</v>
       </c>
       <c r="D4" s="0">
-        <v>-1.4079999999999999</v>
+        <v>-1.306</v>
       </c>
       <c r="E4" s="0">
-        <v>0.16389999999999999</v>
+        <v>0.1961</v>
       </c>
     </row>
   </sheetData>
